--- a/CBRS.xlsx
+++ b/CBRS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D2006D-B5D1-4B78-8A0A-8B0F23A26EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90B18C1-ECC8-49E0-90D9-D81BD9FAF84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{D4AB9EB7-16BE-40D6-9423-80AAF9AE2F0E}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D4AB9EB7-16BE-40D6-9423-80AAF9AE2F0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>Cerebras</t>
   </si>
@@ -171,13 +171,35 @@
   <si>
     <t>Gross Margin</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -229,16 +251,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -594,7 +617,7 @@
         <v>3</v>
       </c>
       <c r="L2">
-        <v>311.07</v>
+        <v>204.45</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -602,10 +625,11 @@
         <v>4</v>
       </c>
       <c r="L3" s="3">
-        <v>215.23</v>
+        <f>92.130188+130.720379+3.682</f>
+        <v>226.532567</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -614,7 +638,7 @@
       </c>
       <c r="L4" s="3">
         <f>+L2*L3</f>
-        <v>66951.596099999995</v>
+        <v>46314.58332315</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -622,11 +646,11 @@
         <v>6</v>
       </c>
       <c r="L5" s="3">
-        <f>701.706+406.531</f>
-        <v>1108.2370000000001</v>
+        <f>1716.016</f>
+        <v>1716.0160000000001</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -637,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -646,7 +670,7 @@
       </c>
       <c r="L7" s="3">
         <f>+L4-L5+L6</f>
-        <v>65843.359100000001</v>
+        <v>44598.567323149997</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -654,8 +678,8 @@
         <v>40</v>
       </c>
       <c r="M10">
-        <f>+L4/Model!G5</f>
-        <v>131.27995611687265</v>
+        <f>+L4/Model!M5</f>
+        <v>90.814511085783863</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -686,45 +710,73 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922091BE-36FB-4AB0-8BD8-E4DD9097BD85}">
-  <dimension ref="A1:CB414"/>
+  <dimension ref="A1:CH414"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:86" x14ac:dyDescent="0.2">
+      <c r="C2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="F2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3">
+        <v>69.674000000000007</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3">
-        <v>211.96499999999997</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>358.44</v>
+        <v>110.593</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="L3" s="3">
+        <v>211.96499999999997</v>
+      </c>
+      <c r="M3" s="3">
+        <v>358.44</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -792,26 +844,36 @@
       <c r="BZ3" s="3"/>
       <c r="CA3" s="3"/>
       <c r="CB3" s="3"/>
-    </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC3" s="3"/>
+      <c r="CD3" s="3"/>
+      <c r="CE3" s="3"/>
+      <c r="CF3" s="3"/>
+      <c r="CG3" s="3"/>
+      <c r="CH3" s="3"/>
+    </row>
+    <row r="4" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3">
+        <v>29.838000000000001</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3">
-        <v>78.286999999999992</v>
-      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>151.55099999999999</v>
+        <v>82.813000000000002</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="L4" s="3">
+        <v>78.286999999999992</v>
+      </c>
+      <c r="M4" s="3">
+        <v>151.55099999999999</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -879,26 +941,36 @@
       <c r="BZ4" s="3"/>
       <c r="CA4" s="3"/>
       <c r="CB4" s="3"/>
-    </row>
-    <row r="5" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC4" s="3"/>
+      <c r="CD4" s="3"/>
+      <c r="CE4" s="3"/>
+      <c r="CF4" s="3"/>
+      <c r="CG4" s="3"/>
+      <c r="CH4" s="3"/>
+    </row>
+    <row r="5" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="5">
+        <v>99.512</v>
+      </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="5">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <v>193.40600000000001</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="5">
         <v>290.25199999999995</v>
       </c>
-      <c r="G5" s="5">
+      <c r="M5" s="5">
         <v>509.99099999999999</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -966,26 +1038,36 @@
       <c r="BZ5" s="3"/>
       <c r="CA5" s="3"/>
       <c r="CB5" s="3"/>
-    </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC5" s="3"/>
+      <c r="CD5" s="3"/>
+      <c r="CE5" s="3"/>
+      <c r="CF5" s="3"/>
+      <c r="CG5" s="3"/>
+      <c r="CH5" s="3"/>
+    </row>
+    <row r="6" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3">
+        <v>48.41</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3">
-        <v>137.30999999999997</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>204.74600000000001</v>
+        <v>64.930999999999997</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="L6" s="3">
+        <v>137.30999999999997</v>
+      </c>
+      <c r="M6" s="3">
+        <v>204.74600000000001</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -1053,26 +1135,36 @@
       <c r="BZ6" s="3"/>
       <c r="CA6" s="3"/>
       <c r="CB6" s="3"/>
-    </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC6" s="3"/>
+      <c r="CD6" s="3"/>
+      <c r="CE6" s="3"/>
+      <c r="CF6" s="3"/>
+      <c r="CG6" s="3"/>
+      <c r="CH6" s="3"/>
+    </row>
+    <row r="7" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3">
+        <v>9.4979999999999993</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>30.204000000000001</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <v>106.17400000000001</v>
+        <v>42.298999999999999</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="3">
+        <v>30.204000000000001</v>
+      </c>
+      <c r="M7" s="3">
+        <v>106.17400000000001</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1140,26 +1232,56 @@
       <c r="BZ7" s="3"/>
       <c r="CA7" s="3"/>
       <c r="CB7" s="3"/>
-    </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC7" s="3"/>
+      <c r="CD7" s="3"/>
+      <c r="CE7" s="3"/>
+      <c r="CF7" s="3"/>
+      <c r="CG7" s="3"/>
+      <c r="CH7" s="3"/>
+    </row>
+    <row r="8" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="C8" s="3">
+        <f t="shared" ref="C8:I8" si="0">+C5-C6-C7</f>
+        <v>41.604000000000006</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="0"/>
+        <v>86.176000000000016</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <f>+J5-J6-J7</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
         <v>122.73799999999996</v>
       </c>
-      <c r="G8" s="3">
+      <c r="M8" s="3">
         <v>199.071</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -1227,26 +1349,36 @@
       <c r="BZ8" s="3"/>
       <c r="CA8" s="3"/>
       <c r="CB8" s="3"/>
-    </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC8" s="3"/>
+      <c r="CD8" s="3"/>
+      <c r="CE8" s="3"/>
+      <c r="CF8" s="3"/>
+      <c r="CG8" s="3"/>
+      <c r="CH8" s="3"/>
+    </row>
+    <row r="9" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3">
+        <v>52.750999999999998</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3">
-        <v>158.23400000000001</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3">
-        <v>243.31900000000002</v>
+        <v>75.495000000000005</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="3">
+        <v>158.23400000000001</v>
+      </c>
+      <c r="M9" s="3">
+        <v>243.31900000000002</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1314,26 +1446,36 @@
       <c r="BZ9" s="3"/>
       <c r="CA9" s="3"/>
       <c r="CB9" s="3"/>
-    </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC9" s="3"/>
+      <c r="CD9" s="3"/>
+      <c r="CE9" s="3"/>
+      <c r="CF9" s="3"/>
+      <c r="CG9" s="3"/>
+      <c r="CH9" s="3"/>
+    </row>
+    <row r="10" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3">
+        <v>10.326000000000001</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3">
-        <v>20.979999999999997</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>76.45</v>
+        <v>14.701000000000001</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="L10" s="3">
+        <v>20.979999999999997</v>
+      </c>
+      <c r="M10" s="3">
+        <v>76.45</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1401,26 +1543,36 @@
       <c r="BZ10" s="3"/>
       <c r="CA10" s="3"/>
       <c r="CB10" s="3"/>
-    </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC10" s="3"/>
+      <c r="CD10" s="3"/>
+      <c r="CE10" s="3"/>
+      <c r="CF10" s="3"/>
+      <c r="CG10" s="3"/>
+      <c r="CH10" s="3"/>
+    </row>
+    <row r="11" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3">
+        <v>6.9969999999999999</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3">
-        <v>44.962000000000003</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <v>30.969000000000001</v>
+        <v>11.016999999999999</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="L11" s="3">
+        <v>44.962000000000003</v>
+      </c>
+      <c r="M11" s="3">
+        <v>30.969000000000001</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1488,26 +1640,56 @@
       <c r="BZ11" s="3"/>
       <c r="CA11" s="3"/>
       <c r="CB11" s="3"/>
-    </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC11" s="3"/>
+      <c r="CD11" s="3"/>
+      <c r="CE11" s="3"/>
+      <c r="CF11" s="3"/>
+      <c r="CG11" s="3"/>
+      <c r="CH11" s="3"/>
+    </row>
+    <row r="12" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="C12" s="3">
+        <f t="shared" ref="C12:F12" si="1">+C8-SUM(C9:C11)</f>
+        <v>-28.469999999999992</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F12" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <f>+G8-SUM(G9:G11)</f>
+        <v>-15.036999999999978</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" ref="H12:J12" si="2">+H8-SUM(H9:H11)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3">
         <v>-101.43800000000006</v>
       </c>
-      <c r="G12" s="3">
+      <c r="M12" s="3">
         <v>-151.66700000000006</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1575,26 +1757,36 @@
       <c r="BZ12" s="3"/>
       <c r="CA12" s="3"/>
       <c r="CB12" s="3"/>
-    </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC12" s="3"/>
+      <c r="CD12" s="3"/>
+      <c r="CE12" s="3"/>
+      <c r="CF12" s="3"/>
+      <c r="CG12" s="3"/>
+      <c r="CH12" s="3"/>
+    </row>
+    <row r="13" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3">
+        <v>6.2859999999999996</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3">
-        <v>-378.23699999999997</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>390.74599999999998</v>
+        <v>2.528</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="L13" s="3">
+        <v>-378.23699999999997</v>
+      </c>
+      <c r="M13" s="3">
+        <v>390.74599999999998</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -1662,26 +1854,47 @@
       <c r="BZ13" s="3"/>
       <c r="CA13" s="3"/>
       <c r="CB13" s="3"/>
-    </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC13" s="3"/>
+      <c r="CD13" s="3"/>
+      <c r="CE13" s="3"/>
+      <c r="CF13" s="3"/>
+      <c r="CG13" s="3"/>
+      <c r="CH13" s="3"/>
+    </row>
+    <row r="14" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="C14" s="3">
+        <f t="shared" ref="C14:F14" si="3">+C12+C13</f>
+        <v>-22.18399999999999</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="F14" s="3">
-        <v>-479.67500000000007</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>239.07899999999992</v>
+        <f>+G12+G13</f>
+        <v>-12.508999999999977</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="L14" s="3">
+        <v>-479.67500000000007</v>
+      </c>
+      <c r="M14" s="3">
+        <v>239.07899999999992</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1749,26 +1962,36 @@
       <c r="BZ14" s="3"/>
       <c r="CA14" s="3"/>
       <c r="CB14" s="3"/>
-    </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC14" s="3"/>
+      <c r="CD14" s="3"/>
+      <c r="CE14" s="3"/>
+      <c r="CF14" s="3"/>
+      <c r="CG14" s="3"/>
+      <c r="CH14" s="3"/>
+    </row>
+    <row r="15" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3">
+        <v>1.6830000000000001</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="3">
-        <v>1.9269999999999998</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>7.0569999999999995</v>
+        <v>1.4970000000000001</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="L15" s="3">
+        <v>1.9269999999999998</v>
+      </c>
+      <c r="M15" s="3">
+        <v>7.0569999999999995</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1836,26 +2059,56 @@
       <c r="BZ15" s="3"/>
       <c r="CA15" s="3"/>
       <c r="CB15" s="3"/>
-    </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC15" s="3"/>
+      <c r="CD15" s="3"/>
+      <c r="CE15" s="3"/>
+      <c r="CF15" s="3"/>
+      <c r="CG15" s="3"/>
+      <c r="CH15" s="3"/>
+    </row>
+    <row r="16" spans="1:86" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="C16" s="3">
+        <f t="shared" ref="C16:F16" si="4">+C14-C15</f>
+        <v>-23.86699999999999</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="F16" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <f>+G14-G15</f>
+        <v>-14.005999999999977</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" ref="H16:J16" si="5">+H14-H15</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
         <v>-481.60200000000009</v>
       </c>
-      <c r="G16" s="3">
+      <c r="M16" s="3">
         <v>232.02199999999993</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -1923,8 +2176,14 @@
       <c r="BZ16" s="3"/>
       <c r="CA16" s="3"/>
       <c r="CB16" s="3"/>
-    </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC16" s="3"/>
+      <c r="CD16" s="3"/>
+      <c r="CE16" s="3"/>
+      <c r="CF16" s="3"/>
+      <c r="CG16" s="3"/>
+      <c r="CH16" s="3"/>
+    </row>
+    <row r="17" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -2003,28 +2262,58 @@
       <c r="BZ17" s="3"/>
       <c r="CA17" s="3"/>
       <c r="CB17" s="3"/>
-    </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC17" s="3"/>
+      <c r="CD17" s="3"/>
+      <c r="CE17" s="3"/>
+      <c r="CF17" s="3"/>
+      <c r="CG17" s="3"/>
+      <c r="CH17" s="3"/>
+    </row>
+    <row r="18" spans="2:86" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3">
-        <f>+F16/F19</f>
+      <c r="C18" s="7">
+        <f t="shared" ref="C18:F18" si="6">+C16/C19</f>
+        <v>-0.45895429109859026</v>
+      </c>
+      <c r="D18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F18" s="7" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="7">
+        <f>+G16/G19</f>
+        <v>-0.22300417157596372</v>
+      </c>
+      <c r="H18" s="7" t="e">
+        <f t="shared" ref="H18:J18" si="7">+H16/H19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I18" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J18" s="7" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3">
+        <f>+L16/L19</f>
         <v>-9.834231805929921</v>
       </c>
-      <c r="G18" s="3">
-        <f>+G16/G19</f>
+      <c r="M18" s="3">
+        <f>+M16/M19</f>
         <v>4.3274768725753496</v>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -2092,26 +2381,36 @@
       <c r="BZ18" s="3"/>
       <c r="CA18" s="3"/>
       <c r="CB18" s="3"/>
-    </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC18" s="3"/>
+      <c r="CD18" s="3"/>
+      <c r="CE18" s="3"/>
+      <c r="CF18" s="3"/>
+      <c r="CG18" s="3"/>
+      <c r="CH18" s="3"/>
+    </row>
+    <row r="19" spans="2:86" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3">
+        <v>52.003</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="3">
-        <v>48.972000000000001</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>53.616</v>
+        <v>62.805999999999997</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="L19" s="3">
+        <v>48.972000000000001</v>
+      </c>
+      <c r="M19" s="3">
+        <v>53.616</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -2179,8 +2478,14 @@
       <c r="BZ19" s="3"/>
       <c r="CA19" s="3"/>
       <c r="CB19" s="3"/>
-    </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC19" s="3"/>
+      <c r="CD19" s="3"/>
+      <c r="CE19" s="3"/>
+      <c r="CF19" s="3"/>
+      <c r="CG19" s="3"/>
+      <c r="CH19" s="3"/>
+    </row>
+    <row r="20" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -2259,8 +2564,14 @@
       <c r="BZ20" s="3"/>
       <c r="CA20" s="3"/>
       <c r="CB20" s="3"/>
-    </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC20" s="3"/>
+      <c r="CD20" s="3"/>
+      <c r="CE20" s="3"/>
+      <c r="CF20" s="3"/>
+      <c r="CG20" s="3"/>
+      <c r="CH20" s="3"/>
+    </row>
+    <row r="21" spans="2:86" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
@@ -2269,15 +2580,18 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="4">
-        <f>+G5/F5-1</f>
-        <v>0.75706282816311377</v>
+        <f>+G5/C5-1</f>
+        <v>0.94354449714607291</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+      <c r="M21" s="4">
+        <f>+M5/L5-1</f>
+        <v>0.75706282816311377</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -2345,28 +2659,55 @@
       <c r="BZ21" s="3"/>
       <c r="CA21" s="3"/>
       <c r="CB21" s="3"/>
-    </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC21" s="3"/>
+      <c r="CD21" s="3"/>
+      <c r="CE21" s="3"/>
+      <c r="CF21" s="3"/>
+      <c r="CG21" s="3"/>
+      <c r="CH21" s="3"/>
+    </row>
+    <row r="22" spans="2:86" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4">
-        <f>+F8/F5</f>
-        <v>0.42286702589473968</v>
+      <c r="C22" s="4">
+        <f t="shared" ref="C22:G22" si="8">+C8/C5</f>
+        <v>0.41808023152986579</v>
+      </c>
+      <c r="D22" s="4" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E22" s="4" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F22" s="4" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="G22" s="4">
         <f>+G8/G5</f>
+        <v>0.44557045800026895</v>
+      </c>
+      <c r="H22" s="4" t="e">
+        <f t="shared" ref="H22:I22" si="9">+H8/H5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I22" s="4" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="4">
+        <f>+L8/L5</f>
+        <v>0.42286702589473968</v>
+      </c>
+      <c r="M22" s="4">
+        <f>+M8/M5</f>
         <v>0.39034218250910313</v>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -2434,8 +2775,14 @@
       <c r="BZ22" s="3"/>
       <c r="CA22" s="3"/>
       <c r="CB22" s="3"/>
-    </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC22" s="3"/>
+      <c r="CD22" s="3"/>
+      <c r="CE22" s="3"/>
+      <c r="CF22" s="3"/>
+      <c r="CG22" s="3"/>
+      <c r="CH22" s="3"/>
+    </row>
+    <row r="23" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -2514,8 +2861,14 @@
       <c r="BZ23" s="3"/>
       <c r="CA23" s="3"/>
       <c r="CB23" s="3"/>
-    </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC23" s="3"/>
+      <c r="CD23" s="3"/>
+      <c r="CE23" s="3"/>
+      <c r="CF23" s="3"/>
+      <c r="CG23" s="3"/>
+      <c r="CH23" s="3"/>
+    </row>
+    <row r="24" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -2594,8 +2947,14 @@
       <c r="BZ24" s="3"/>
       <c r="CA24" s="3"/>
       <c r="CB24" s="3"/>
-    </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC24" s="3"/>
+      <c r="CD24" s="3"/>
+      <c r="CE24" s="3"/>
+      <c r="CF24" s="3"/>
+      <c r="CG24" s="3"/>
+      <c r="CH24" s="3"/>
+    </row>
+    <row r="25" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -2674,8 +3033,14 @@
       <c r="BZ25" s="3"/>
       <c r="CA25" s="3"/>
       <c r="CB25" s="3"/>
-    </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC25" s="3"/>
+      <c r="CD25" s="3"/>
+      <c r="CE25" s="3"/>
+      <c r="CF25" s="3"/>
+      <c r="CG25" s="3"/>
+      <c r="CH25" s="3"/>
+    </row>
+    <row r="26" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -2754,8 +3119,14 @@
       <c r="BZ26" s="3"/>
       <c r="CA26" s="3"/>
       <c r="CB26" s="3"/>
-    </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC26" s="3"/>
+      <c r="CD26" s="3"/>
+      <c r="CE26" s="3"/>
+      <c r="CF26" s="3"/>
+      <c r="CG26" s="3"/>
+      <c r="CH26" s="3"/>
+    </row>
+    <row r="27" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2834,8 +3205,14 @@
       <c r="BZ27" s="3"/>
       <c r="CA27" s="3"/>
       <c r="CB27" s="3"/>
-    </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC27" s="3"/>
+      <c r="CD27" s="3"/>
+      <c r="CE27" s="3"/>
+      <c r="CF27" s="3"/>
+      <c r="CG27" s="3"/>
+      <c r="CH27" s="3"/>
+    </row>
+    <row r="28" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2914,8 +3291,14 @@
       <c r="BZ28" s="3"/>
       <c r="CA28" s="3"/>
       <c r="CB28" s="3"/>
-    </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC28" s="3"/>
+      <c r="CD28" s="3"/>
+      <c r="CE28" s="3"/>
+      <c r="CF28" s="3"/>
+      <c r="CG28" s="3"/>
+      <c r="CH28" s="3"/>
+    </row>
+    <row r="29" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -2994,8 +3377,14 @@
       <c r="BZ29" s="3"/>
       <c r="CA29" s="3"/>
       <c r="CB29" s="3"/>
-    </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC29" s="3"/>
+      <c r="CD29" s="3"/>
+      <c r="CE29" s="3"/>
+      <c r="CF29" s="3"/>
+      <c r="CG29" s="3"/>
+      <c r="CH29" s="3"/>
+    </row>
+    <row r="30" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -3074,8 +3463,14 @@
       <c r="BZ30" s="3"/>
       <c r="CA30" s="3"/>
       <c r="CB30" s="3"/>
-    </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC30" s="3"/>
+      <c r="CD30" s="3"/>
+      <c r="CE30" s="3"/>
+      <c r="CF30" s="3"/>
+      <c r="CG30" s="3"/>
+      <c r="CH30" s="3"/>
+    </row>
+    <row r="31" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -3154,8 +3549,14 @@
       <c r="BZ31" s="3"/>
       <c r="CA31" s="3"/>
       <c r="CB31" s="3"/>
-    </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC31" s="3"/>
+      <c r="CD31" s="3"/>
+      <c r="CE31" s="3"/>
+      <c r="CF31" s="3"/>
+      <c r="CG31" s="3"/>
+      <c r="CH31" s="3"/>
+    </row>
+    <row r="32" spans="2:86" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -3234,8 +3635,14 @@
       <c r="BZ32" s="3"/>
       <c r="CA32" s="3"/>
       <c r="CB32" s="3"/>
-    </row>
-    <row r="33" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC32" s="3"/>
+      <c r="CD32" s="3"/>
+      <c r="CE32" s="3"/>
+      <c r="CF32" s="3"/>
+      <c r="CG32" s="3"/>
+      <c r="CH32" s="3"/>
+    </row>
+    <row r="33" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -3314,8 +3721,14 @@
       <c r="BZ33" s="3"/>
       <c r="CA33" s="3"/>
       <c r="CB33" s="3"/>
-    </row>
-    <row r="34" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC33" s="3"/>
+      <c r="CD33" s="3"/>
+      <c r="CE33" s="3"/>
+      <c r="CF33" s="3"/>
+      <c r="CG33" s="3"/>
+      <c r="CH33" s="3"/>
+    </row>
+    <row r="34" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -3394,8 +3807,14 @@
       <c r="BZ34" s="3"/>
       <c r="CA34" s="3"/>
       <c r="CB34" s="3"/>
-    </row>
-    <row r="35" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC34" s="3"/>
+      <c r="CD34" s="3"/>
+      <c r="CE34" s="3"/>
+      <c r="CF34" s="3"/>
+      <c r="CG34" s="3"/>
+      <c r="CH34" s="3"/>
+    </row>
+    <row r="35" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -3474,8 +3893,14 @@
       <c r="BZ35" s="3"/>
       <c r="CA35" s="3"/>
       <c r="CB35" s="3"/>
-    </row>
-    <row r="36" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC35" s="3"/>
+      <c r="CD35" s="3"/>
+      <c r="CE35" s="3"/>
+      <c r="CF35" s="3"/>
+      <c r="CG35" s="3"/>
+      <c r="CH35" s="3"/>
+    </row>
+    <row r="36" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -3554,8 +3979,14 @@
       <c r="BZ36" s="3"/>
       <c r="CA36" s="3"/>
       <c r="CB36" s="3"/>
-    </row>
-    <row r="37" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC36" s="3"/>
+      <c r="CD36" s="3"/>
+      <c r="CE36" s="3"/>
+      <c r="CF36" s="3"/>
+      <c r="CG36" s="3"/>
+      <c r="CH36" s="3"/>
+    </row>
+    <row r="37" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -3634,8 +4065,14 @@
       <c r="BZ37" s="3"/>
       <c r="CA37" s="3"/>
       <c r="CB37" s="3"/>
-    </row>
-    <row r="38" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC37" s="3"/>
+      <c r="CD37" s="3"/>
+      <c r="CE37" s="3"/>
+      <c r="CF37" s="3"/>
+      <c r="CG37" s="3"/>
+      <c r="CH37" s="3"/>
+    </row>
+    <row r="38" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3714,8 +4151,14 @@
       <c r="BZ38" s="3"/>
       <c r="CA38" s="3"/>
       <c r="CB38" s="3"/>
-    </row>
-    <row r="39" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC38" s="3"/>
+      <c r="CD38" s="3"/>
+      <c r="CE38" s="3"/>
+      <c r="CF38" s="3"/>
+      <c r="CG38" s="3"/>
+      <c r="CH38" s="3"/>
+    </row>
+    <row r="39" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3794,8 +4237,14 @@
       <c r="BZ39" s="3"/>
       <c r="CA39" s="3"/>
       <c r="CB39" s="3"/>
-    </row>
-    <row r="40" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC39" s="3"/>
+      <c r="CD39" s="3"/>
+      <c r="CE39" s="3"/>
+      <c r="CF39" s="3"/>
+      <c r="CG39" s="3"/>
+      <c r="CH39" s="3"/>
+    </row>
+    <row r="40" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3874,8 +4323,14 @@
       <c r="BZ40" s="3"/>
       <c r="CA40" s="3"/>
       <c r="CB40" s="3"/>
-    </row>
-    <row r="41" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC40" s="3"/>
+      <c r="CD40" s="3"/>
+      <c r="CE40" s="3"/>
+      <c r="CF40" s="3"/>
+      <c r="CG40" s="3"/>
+      <c r="CH40" s="3"/>
+    </row>
+    <row r="41" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3954,8 +4409,14 @@
       <c r="BZ41" s="3"/>
       <c r="CA41" s="3"/>
       <c r="CB41" s="3"/>
-    </row>
-    <row r="42" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC41" s="3"/>
+      <c r="CD41" s="3"/>
+      <c r="CE41" s="3"/>
+      <c r="CF41" s="3"/>
+      <c r="CG41" s="3"/>
+      <c r="CH41" s="3"/>
+    </row>
+    <row r="42" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -4034,8 +4495,14 @@
       <c r="BZ42" s="3"/>
       <c r="CA42" s="3"/>
       <c r="CB42" s="3"/>
-    </row>
-    <row r="43" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC42" s="3"/>
+      <c r="CD42" s="3"/>
+      <c r="CE42" s="3"/>
+      <c r="CF42" s="3"/>
+      <c r="CG42" s="3"/>
+      <c r="CH42" s="3"/>
+    </row>
+    <row r="43" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -4114,8 +4581,14 @@
       <c r="BZ43" s="3"/>
       <c r="CA43" s="3"/>
       <c r="CB43" s="3"/>
-    </row>
-    <row r="44" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC43" s="3"/>
+      <c r="CD43" s="3"/>
+      <c r="CE43" s="3"/>
+      <c r="CF43" s="3"/>
+      <c r="CG43" s="3"/>
+      <c r="CH43" s="3"/>
+    </row>
+    <row r="44" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -4194,8 +4667,14 @@
       <c r="BZ44" s="3"/>
       <c r="CA44" s="3"/>
       <c r="CB44" s="3"/>
-    </row>
-    <row r="45" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC44" s="3"/>
+      <c r="CD44" s="3"/>
+      <c r="CE44" s="3"/>
+      <c r="CF44" s="3"/>
+      <c r="CG44" s="3"/>
+      <c r="CH44" s="3"/>
+    </row>
+    <row r="45" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4274,8 +4753,14 @@
       <c r="BZ45" s="3"/>
       <c r="CA45" s="3"/>
       <c r="CB45" s="3"/>
-    </row>
-    <row r="46" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC45" s="3"/>
+      <c r="CD45" s="3"/>
+      <c r="CE45" s="3"/>
+      <c r="CF45" s="3"/>
+      <c r="CG45" s="3"/>
+      <c r="CH45" s="3"/>
+    </row>
+    <row r="46" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -4354,8 +4839,14 @@
       <c r="BZ46" s="3"/>
       <c r="CA46" s="3"/>
       <c r="CB46" s="3"/>
-    </row>
-    <row r="47" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC46" s="3"/>
+      <c r="CD46" s="3"/>
+      <c r="CE46" s="3"/>
+      <c r="CF46" s="3"/>
+      <c r="CG46" s="3"/>
+      <c r="CH46" s="3"/>
+    </row>
+    <row r="47" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -4434,8 +4925,14 @@
       <c r="BZ47" s="3"/>
       <c r="CA47" s="3"/>
       <c r="CB47" s="3"/>
-    </row>
-    <row r="48" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC47" s="3"/>
+      <c r="CD47" s="3"/>
+      <c r="CE47" s="3"/>
+      <c r="CF47" s="3"/>
+      <c r="CG47" s="3"/>
+      <c r="CH47" s="3"/>
+    </row>
+    <row r="48" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4514,8 +5011,14 @@
       <c r="BZ48" s="3"/>
       <c r="CA48" s="3"/>
       <c r="CB48" s="3"/>
-    </row>
-    <row r="49" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC48" s="3"/>
+      <c r="CD48" s="3"/>
+      <c r="CE48" s="3"/>
+      <c r="CF48" s="3"/>
+      <c r="CG48" s="3"/>
+      <c r="CH48" s="3"/>
+    </row>
+    <row r="49" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -4594,8 +5097,14 @@
       <c r="BZ49" s="3"/>
       <c r="CA49" s="3"/>
       <c r="CB49" s="3"/>
-    </row>
-    <row r="50" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC49" s="3"/>
+      <c r="CD49" s="3"/>
+      <c r="CE49" s="3"/>
+      <c r="CF49" s="3"/>
+      <c r="CG49" s="3"/>
+      <c r="CH49" s="3"/>
+    </row>
+    <row r="50" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -4674,8 +5183,14 @@
       <c r="BZ50" s="3"/>
       <c r="CA50" s="3"/>
       <c r="CB50" s="3"/>
-    </row>
-    <row r="51" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC50" s="3"/>
+      <c r="CD50" s="3"/>
+      <c r="CE50" s="3"/>
+      <c r="CF50" s="3"/>
+      <c r="CG50" s="3"/>
+      <c r="CH50" s="3"/>
+    </row>
+    <row r="51" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -4754,8 +5269,14 @@
       <c r="BZ51" s="3"/>
       <c r="CA51" s="3"/>
       <c r="CB51" s="3"/>
-    </row>
-    <row r="52" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC51" s="3"/>
+      <c r="CD51" s="3"/>
+      <c r="CE51" s="3"/>
+      <c r="CF51" s="3"/>
+      <c r="CG51" s="3"/>
+      <c r="CH51" s="3"/>
+    </row>
+    <row r="52" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -4834,8 +5355,14 @@
       <c r="BZ52" s="3"/>
       <c r="CA52" s="3"/>
       <c r="CB52" s="3"/>
-    </row>
-    <row r="53" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC52" s="3"/>
+      <c r="CD52" s="3"/>
+      <c r="CE52" s="3"/>
+      <c r="CF52" s="3"/>
+      <c r="CG52" s="3"/>
+      <c r="CH52" s="3"/>
+    </row>
+    <row r="53" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -4914,8 +5441,14 @@
       <c r="BZ53" s="3"/>
       <c r="CA53" s="3"/>
       <c r="CB53" s="3"/>
-    </row>
-    <row r="54" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC53" s="3"/>
+      <c r="CD53" s="3"/>
+      <c r="CE53" s="3"/>
+      <c r="CF53" s="3"/>
+      <c r="CG53" s="3"/>
+      <c r="CH53" s="3"/>
+    </row>
+    <row r="54" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -4994,8 +5527,14 @@
       <c r="BZ54" s="3"/>
       <c r="CA54" s="3"/>
       <c r="CB54" s="3"/>
-    </row>
-    <row r="55" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC54" s="3"/>
+      <c r="CD54" s="3"/>
+      <c r="CE54" s="3"/>
+      <c r="CF54" s="3"/>
+      <c r="CG54" s="3"/>
+      <c r="CH54" s="3"/>
+    </row>
+    <row r="55" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -5074,8 +5613,14 @@
       <c r="BZ55" s="3"/>
       <c r="CA55" s="3"/>
       <c r="CB55" s="3"/>
-    </row>
-    <row r="56" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC55" s="3"/>
+      <c r="CD55" s="3"/>
+      <c r="CE55" s="3"/>
+      <c r="CF55" s="3"/>
+      <c r="CG55" s="3"/>
+      <c r="CH55" s="3"/>
+    </row>
+    <row r="56" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -5154,8 +5699,14 @@
       <c r="BZ56" s="3"/>
       <c r="CA56" s="3"/>
       <c r="CB56" s="3"/>
-    </row>
-    <row r="57" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC56" s="3"/>
+      <c r="CD56" s="3"/>
+      <c r="CE56" s="3"/>
+      <c r="CF56" s="3"/>
+      <c r="CG56" s="3"/>
+      <c r="CH56" s="3"/>
+    </row>
+    <row r="57" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -5234,8 +5785,14 @@
       <c r="BZ57" s="3"/>
       <c r="CA57" s="3"/>
       <c r="CB57" s="3"/>
-    </row>
-    <row r="58" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC57" s="3"/>
+      <c r="CD57" s="3"/>
+      <c r="CE57" s="3"/>
+      <c r="CF57" s="3"/>
+      <c r="CG57" s="3"/>
+      <c r="CH57" s="3"/>
+    </row>
+    <row r="58" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -5314,8 +5871,14 @@
       <c r="BZ58" s="3"/>
       <c r="CA58" s="3"/>
       <c r="CB58" s="3"/>
-    </row>
-    <row r="59" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC58" s="3"/>
+      <c r="CD58" s="3"/>
+      <c r="CE58" s="3"/>
+      <c r="CF58" s="3"/>
+      <c r="CG58" s="3"/>
+      <c r="CH58" s="3"/>
+    </row>
+    <row r="59" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -5394,8 +5957,14 @@
       <c r="BZ59" s="3"/>
       <c r="CA59" s="3"/>
       <c r="CB59" s="3"/>
-    </row>
-    <row r="60" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC59" s="3"/>
+      <c r="CD59" s="3"/>
+      <c r="CE59" s="3"/>
+      <c r="CF59" s="3"/>
+      <c r="CG59" s="3"/>
+      <c r="CH59" s="3"/>
+    </row>
+    <row r="60" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -5474,8 +6043,14 @@
       <c r="BZ60" s="3"/>
       <c r="CA60" s="3"/>
       <c r="CB60" s="3"/>
-    </row>
-    <row r="61" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC60" s="3"/>
+      <c r="CD60" s="3"/>
+      <c r="CE60" s="3"/>
+      <c r="CF60" s="3"/>
+      <c r="CG60" s="3"/>
+      <c r="CH60" s="3"/>
+    </row>
+    <row r="61" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -5554,8 +6129,14 @@
       <c r="BZ61" s="3"/>
       <c r="CA61" s="3"/>
       <c r="CB61" s="3"/>
-    </row>
-    <row r="62" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC61" s="3"/>
+      <c r="CD61" s="3"/>
+      <c r="CE61" s="3"/>
+      <c r="CF61" s="3"/>
+      <c r="CG61" s="3"/>
+      <c r="CH61" s="3"/>
+    </row>
+    <row r="62" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -5634,8 +6215,14 @@
       <c r="BZ62" s="3"/>
       <c r="CA62" s="3"/>
       <c r="CB62" s="3"/>
-    </row>
-    <row r="63" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC62" s="3"/>
+      <c r="CD62" s="3"/>
+      <c r="CE62" s="3"/>
+      <c r="CF62" s="3"/>
+      <c r="CG62" s="3"/>
+      <c r="CH62" s="3"/>
+    </row>
+    <row r="63" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -5714,8 +6301,14 @@
       <c r="BZ63" s="3"/>
       <c r="CA63" s="3"/>
       <c r="CB63" s="3"/>
-    </row>
-    <row r="64" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC63" s="3"/>
+      <c r="CD63" s="3"/>
+      <c r="CE63" s="3"/>
+      <c r="CF63" s="3"/>
+      <c r="CG63" s="3"/>
+      <c r="CH63" s="3"/>
+    </row>
+    <row r="64" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -5794,8 +6387,14 @@
       <c r="BZ64" s="3"/>
       <c r="CA64" s="3"/>
       <c r="CB64" s="3"/>
-    </row>
-    <row r="65" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC64" s="3"/>
+      <c r="CD64" s="3"/>
+      <c r="CE64" s="3"/>
+      <c r="CF64" s="3"/>
+      <c r="CG64" s="3"/>
+      <c r="CH64" s="3"/>
+    </row>
+    <row r="65" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -5874,8 +6473,14 @@
       <c r="BZ65" s="3"/>
       <c r="CA65" s="3"/>
       <c r="CB65" s="3"/>
-    </row>
-    <row r="66" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC65" s="3"/>
+      <c r="CD65" s="3"/>
+      <c r="CE65" s="3"/>
+      <c r="CF65" s="3"/>
+      <c r="CG65" s="3"/>
+      <c r="CH65" s="3"/>
+    </row>
+    <row r="66" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -5954,8 +6559,14 @@
       <c r="BZ66" s="3"/>
       <c r="CA66" s="3"/>
       <c r="CB66" s="3"/>
-    </row>
-    <row r="67" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC66" s="3"/>
+      <c r="CD66" s="3"/>
+      <c r="CE66" s="3"/>
+      <c r="CF66" s="3"/>
+      <c r="CG66" s="3"/>
+      <c r="CH66" s="3"/>
+    </row>
+    <row r="67" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -6034,8 +6645,14 @@
       <c r="BZ67" s="3"/>
       <c r="CA67" s="3"/>
       <c r="CB67" s="3"/>
-    </row>
-    <row r="68" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC67" s="3"/>
+      <c r="CD67" s="3"/>
+      <c r="CE67" s="3"/>
+      <c r="CF67" s="3"/>
+      <c r="CG67" s="3"/>
+      <c r="CH67" s="3"/>
+    </row>
+    <row r="68" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -6114,8 +6731,14 @@
       <c r="BZ68" s="3"/>
       <c r="CA68" s="3"/>
       <c r="CB68" s="3"/>
-    </row>
-    <row r="69" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC68" s="3"/>
+      <c r="CD68" s="3"/>
+      <c r="CE68" s="3"/>
+      <c r="CF68" s="3"/>
+      <c r="CG68" s="3"/>
+      <c r="CH68" s="3"/>
+    </row>
+    <row r="69" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -6194,8 +6817,14 @@
       <c r="BZ69" s="3"/>
       <c r="CA69" s="3"/>
       <c r="CB69" s="3"/>
-    </row>
-    <row r="70" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC69" s="3"/>
+      <c r="CD69" s="3"/>
+      <c r="CE69" s="3"/>
+      <c r="CF69" s="3"/>
+      <c r="CG69" s="3"/>
+      <c r="CH69" s="3"/>
+    </row>
+    <row r="70" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -6274,8 +6903,14 @@
       <c r="BZ70" s="3"/>
       <c r="CA70" s="3"/>
       <c r="CB70" s="3"/>
-    </row>
-    <row r="71" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC70" s="3"/>
+      <c r="CD70" s="3"/>
+      <c r="CE70" s="3"/>
+      <c r="CF70" s="3"/>
+      <c r="CG70" s="3"/>
+      <c r="CH70" s="3"/>
+    </row>
+    <row r="71" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -6354,8 +6989,14 @@
       <c r="BZ71" s="3"/>
       <c r="CA71" s="3"/>
       <c r="CB71" s="3"/>
-    </row>
-    <row r="72" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC71" s="3"/>
+      <c r="CD71" s="3"/>
+      <c r="CE71" s="3"/>
+      <c r="CF71" s="3"/>
+      <c r="CG71" s="3"/>
+      <c r="CH71" s="3"/>
+    </row>
+    <row r="72" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -6434,8 +7075,14 @@
       <c r="BZ72" s="3"/>
       <c r="CA72" s="3"/>
       <c r="CB72" s="3"/>
-    </row>
-    <row r="73" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC72" s="3"/>
+      <c r="CD72" s="3"/>
+      <c r="CE72" s="3"/>
+      <c r="CF72" s="3"/>
+      <c r="CG72" s="3"/>
+      <c r="CH72" s="3"/>
+    </row>
+    <row r="73" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -6514,8 +7161,14 @@
       <c r="BZ73" s="3"/>
       <c r="CA73" s="3"/>
       <c r="CB73" s="3"/>
-    </row>
-    <row r="74" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC73" s="3"/>
+      <c r="CD73" s="3"/>
+      <c r="CE73" s="3"/>
+      <c r="CF73" s="3"/>
+      <c r="CG73" s="3"/>
+      <c r="CH73" s="3"/>
+    </row>
+    <row r="74" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -6594,8 +7247,14 @@
       <c r="BZ74" s="3"/>
       <c r="CA74" s="3"/>
       <c r="CB74" s="3"/>
-    </row>
-    <row r="75" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC74" s="3"/>
+      <c r="CD74" s="3"/>
+      <c r="CE74" s="3"/>
+      <c r="CF74" s="3"/>
+      <c r="CG74" s="3"/>
+      <c r="CH74" s="3"/>
+    </row>
+    <row r="75" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6674,8 +7333,14 @@
       <c r="BZ75" s="3"/>
       <c r="CA75" s="3"/>
       <c r="CB75" s="3"/>
-    </row>
-    <row r="76" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC75" s="3"/>
+      <c r="CD75" s="3"/>
+      <c r="CE75" s="3"/>
+      <c r="CF75" s="3"/>
+      <c r="CG75" s="3"/>
+      <c r="CH75" s="3"/>
+    </row>
+    <row r="76" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -6754,8 +7419,14 @@
       <c r="BZ76" s="3"/>
       <c r="CA76" s="3"/>
       <c r="CB76" s="3"/>
-    </row>
-    <row r="77" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC76" s="3"/>
+      <c r="CD76" s="3"/>
+      <c r="CE76" s="3"/>
+      <c r="CF76" s="3"/>
+      <c r="CG76" s="3"/>
+      <c r="CH76" s="3"/>
+    </row>
+    <row r="77" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -6834,8 +7505,14 @@
       <c r="BZ77" s="3"/>
       <c r="CA77" s="3"/>
       <c r="CB77" s="3"/>
-    </row>
-    <row r="78" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC77" s="3"/>
+      <c r="CD77" s="3"/>
+      <c r="CE77" s="3"/>
+      <c r="CF77" s="3"/>
+      <c r="CG77" s="3"/>
+      <c r="CH77" s="3"/>
+    </row>
+    <row r="78" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -6914,8 +7591,14 @@
       <c r="BZ78" s="3"/>
       <c r="CA78" s="3"/>
       <c r="CB78" s="3"/>
-    </row>
-    <row r="79" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC78" s="3"/>
+      <c r="CD78" s="3"/>
+      <c r="CE78" s="3"/>
+      <c r="CF78" s="3"/>
+      <c r="CG78" s="3"/>
+      <c r="CH78" s="3"/>
+    </row>
+    <row r="79" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -6994,8 +7677,14 @@
       <c r="BZ79" s="3"/>
       <c r="CA79" s="3"/>
       <c r="CB79" s="3"/>
-    </row>
-    <row r="80" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC79" s="3"/>
+      <c r="CD79" s="3"/>
+      <c r="CE79" s="3"/>
+      <c r="CF79" s="3"/>
+      <c r="CG79" s="3"/>
+      <c r="CH79" s="3"/>
+    </row>
+    <row r="80" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -7074,8 +7763,14 @@
       <c r="BZ80" s="3"/>
       <c r="CA80" s="3"/>
       <c r="CB80" s="3"/>
-    </row>
-    <row r="81" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC80" s="3"/>
+      <c r="CD80" s="3"/>
+      <c r="CE80" s="3"/>
+      <c r="CF80" s="3"/>
+      <c r="CG80" s="3"/>
+      <c r="CH80" s="3"/>
+    </row>
+    <row r="81" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -7154,8 +7849,14 @@
       <c r="BZ81" s="3"/>
       <c r="CA81" s="3"/>
       <c r="CB81" s="3"/>
-    </row>
-    <row r="82" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC81" s="3"/>
+      <c r="CD81" s="3"/>
+      <c r="CE81" s="3"/>
+      <c r="CF81" s="3"/>
+      <c r="CG81" s="3"/>
+      <c r="CH81" s="3"/>
+    </row>
+    <row r="82" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -7234,8 +7935,14 @@
       <c r="BZ82" s="3"/>
       <c r="CA82" s="3"/>
       <c r="CB82" s="3"/>
-    </row>
-    <row r="83" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC82" s="3"/>
+      <c r="CD82" s="3"/>
+      <c r="CE82" s="3"/>
+      <c r="CF82" s="3"/>
+      <c r="CG82" s="3"/>
+      <c r="CH82" s="3"/>
+    </row>
+    <row r="83" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -7314,8 +8021,14 @@
       <c r="BZ83" s="3"/>
       <c r="CA83" s="3"/>
       <c r="CB83" s="3"/>
-    </row>
-    <row r="84" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC83" s="3"/>
+      <c r="CD83" s="3"/>
+      <c r="CE83" s="3"/>
+      <c r="CF83" s="3"/>
+      <c r="CG83" s="3"/>
+      <c r="CH83" s="3"/>
+    </row>
+    <row r="84" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -7394,8 +8107,14 @@
       <c r="BZ84" s="3"/>
       <c r="CA84" s="3"/>
       <c r="CB84" s="3"/>
-    </row>
-    <row r="85" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC84" s="3"/>
+      <c r="CD84" s="3"/>
+      <c r="CE84" s="3"/>
+      <c r="CF84" s="3"/>
+      <c r="CG84" s="3"/>
+      <c r="CH84" s="3"/>
+    </row>
+    <row r="85" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -7474,8 +8193,14 @@
       <c r="BZ85" s="3"/>
       <c r="CA85" s="3"/>
       <c r="CB85" s="3"/>
-    </row>
-    <row r="86" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC85" s="3"/>
+      <c r="CD85" s="3"/>
+      <c r="CE85" s="3"/>
+      <c r="CF85" s="3"/>
+      <c r="CG85" s="3"/>
+      <c r="CH85" s="3"/>
+    </row>
+    <row r="86" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -7554,8 +8279,14 @@
       <c r="BZ86" s="3"/>
       <c r="CA86" s="3"/>
       <c r="CB86" s="3"/>
-    </row>
-    <row r="87" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC86" s="3"/>
+      <c r="CD86" s="3"/>
+      <c r="CE86" s="3"/>
+      <c r="CF86" s="3"/>
+      <c r="CG86" s="3"/>
+      <c r="CH86" s="3"/>
+    </row>
+    <row r="87" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -7634,8 +8365,14 @@
       <c r="BZ87" s="3"/>
       <c r="CA87" s="3"/>
       <c r="CB87" s="3"/>
-    </row>
-    <row r="88" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC87" s="3"/>
+      <c r="CD87" s="3"/>
+      <c r="CE87" s="3"/>
+      <c r="CF87" s="3"/>
+      <c r="CG87" s="3"/>
+      <c r="CH87" s="3"/>
+    </row>
+    <row r="88" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -7714,8 +8451,14 @@
       <c r="BZ88" s="3"/>
       <c r="CA88" s="3"/>
       <c r="CB88" s="3"/>
-    </row>
-    <row r="89" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC88" s="3"/>
+      <c r="CD88" s="3"/>
+      <c r="CE88" s="3"/>
+      <c r="CF88" s="3"/>
+      <c r="CG88" s="3"/>
+      <c r="CH88" s="3"/>
+    </row>
+    <row r="89" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -7794,8 +8537,14 @@
       <c r="BZ89" s="3"/>
       <c r="CA89" s="3"/>
       <c r="CB89" s="3"/>
-    </row>
-    <row r="90" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC89" s="3"/>
+      <c r="CD89" s="3"/>
+      <c r="CE89" s="3"/>
+      <c r="CF89" s="3"/>
+      <c r="CG89" s="3"/>
+      <c r="CH89" s="3"/>
+    </row>
+    <row r="90" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -7874,8 +8623,14 @@
       <c r="BZ90" s="3"/>
       <c r="CA90" s="3"/>
       <c r="CB90" s="3"/>
-    </row>
-    <row r="91" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC90" s="3"/>
+      <c r="CD90" s="3"/>
+      <c r="CE90" s="3"/>
+      <c r="CF90" s="3"/>
+      <c r="CG90" s="3"/>
+      <c r="CH90" s="3"/>
+    </row>
+    <row r="91" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -7954,8 +8709,14 @@
       <c r="BZ91" s="3"/>
       <c r="CA91" s="3"/>
       <c r="CB91" s="3"/>
-    </row>
-    <row r="92" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC91" s="3"/>
+      <c r="CD91" s="3"/>
+      <c r="CE91" s="3"/>
+      <c r="CF91" s="3"/>
+      <c r="CG91" s="3"/>
+      <c r="CH91" s="3"/>
+    </row>
+    <row r="92" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -8034,8 +8795,14 @@
       <c r="BZ92" s="3"/>
       <c r="CA92" s="3"/>
       <c r="CB92" s="3"/>
-    </row>
-    <row r="93" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC92" s="3"/>
+      <c r="CD92" s="3"/>
+      <c r="CE92" s="3"/>
+      <c r="CF92" s="3"/>
+      <c r="CG92" s="3"/>
+      <c r="CH92" s="3"/>
+    </row>
+    <row r="93" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -8114,8 +8881,14 @@
       <c r="BZ93" s="3"/>
       <c r="CA93" s="3"/>
       <c r="CB93" s="3"/>
-    </row>
-    <row r="94" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC93" s="3"/>
+      <c r="CD93" s="3"/>
+      <c r="CE93" s="3"/>
+      <c r="CF93" s="3"/>
+      <c r="CG93" s="3"/>
+      <c r="CH93" s="3"/>
+    </row>
+    <row r="94" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -8194,8 +8967,14 @@
       <c r="BZ94" s="3"/>
       <c r="CA94" s="3"/>
       <c r="CB94" s="3"/>
-    </row>
-    <row r="95" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC94" s="3"/>
+      <c r="CD94" s="3"/>
+      <c r="CE94" s="3"/>
+      <c r="CF94" s="3"/>
+      <c r="CG94" s="3"/>
+      <c r="CH94" s="3"/>
+    </row>
+    <row r="95" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -8274,8 +9053,14 @@
       <c r="BZ95" s="3"/>
       <c r="CA95" s="3"/>
       <c r="CB95" s="3"/>
-    </row>
-    <row r="96" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC95" s="3"/>
+      <c r="CD95" s="3"/>
+      <c r="CE95" s="3"/>
+      <c r="CF95" s="3"/>
+      <c r="CG95" s="3"/>
+      <c r="CH95" s="3"/>
+    </row>
+    <row r="96" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -8354,8 +9139,14 @@
       <c r="BZ96" s="3"/>
       <c r="CA96" s="3"/>
       <c r="CB96" s="3"/>
-    </row>
-    <row r="97" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC96" s="3"/>
+      <c r="CD96" s="3"/>
+      <c r="CE96" s="3"/>
+      <c r="CF96" s="3"/>
+      <c r="CG96" s="3"/>
+      <c r="CH96" s="3"/>
+    </row>
+    <row r="97" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -8434,8 +9225,14 @@
       <c r="BZ97" s="3"/>
       <c r="CA97" s="3"/>
       <c r="CB97" s="3"/>
-    </row>
-    <row r="98" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC97" s="3"/>
+      <c r="CD97" s="3"/>
+      <c r="CE97" s="3"/>
+      <c r="CF97" s="3"/>
+      <c r="CG97" s="3"/>
+      <c r="CH97" s="3"/>
+    </row>
+    <row r="98" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -8514,8 +9311,14 @@
       <c r="BZ98" s="3"/>
       <c r="CA98" s="3"/>
       <c r="CB98" s="3"/>
-    </row>
-    <row r="99" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC98" s="3"/>
+      <c r="CD98" s="3"/>
+      <c r="CE98" s="3"/>
+      <c r="CF98" s="3"/>
+      <c r="CG98" s="3"/>
+      <c r="CH98" s="3"/>
+    </row>
+    <row r="99" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -8594,8 +9397,14 @@
       <c r="BZ99" s="3"/>
       <c r="CA99" s="3"/>
       <c r="CB99" s="3"/>
-    </row>
-    <row r="100" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC99" s="3"/>
+      <c r="CD99" s="3"/>
+      <c r="CE99" s="3"/>
+      <c r="CF99" s="3"/>
+      <c r="CG99" s="3"/>
+      <c r="CH99" s="3"/>
+    </row>
+    <row r="100" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -8674,8 +9483,14 @@
       <c r="BZ100" s="3"/>
       <c r="CA100" s="3"/>
       <c r="CB100" s="3"/>
-    </row>
-    <row r="101" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC100" s="3"/>
+      <c r="CD100" s="3"/>
+      <c r="CE100" s="3"/>
+      <c r="CF100" s="3"/>
+      <c r="CG100" s="3"/>
+      <c r="CH100" s="3"/>
+    </row>
+    <row r="101" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -8754,8 +9569,14 @@
       <c r="BZ101" s="3"/>
       <c r="CA101" s="3"/>
       <c r="CB101" s="3"/>
-    </row>
-    <row r="102" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC101" s="3"/>
+      <c r="CD101" s="3"/>
+      <c r="CE101" s="3"/>
+      <c r="CF101" s="3"/>
+      <c r="CG101" s="3"/>
+      <c r="CH101" s="3"/>
+    </row>
+    <row r="102" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -8834,8 +9655,14 @@
       <c r="BZ102" s="3"/>
       <c r="CA102" s="3"/>
       <c r="CB102" s="3"/>
-    </row>
-    <row r="103" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC102" s="3"/>
+      <c r="CD102" s="3"/>
+      <c r="CE102" s="3"/>
+      <c r="CF102" s="3"/>
+      <c r="CG102" s="3"/>
+      <c r="CH102" s="3"/>
+    </row>
+    <row r="103" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -8914,8 +9741,14 @@
       <c r="BZ103" s="3"/>
       <c r="CA103" s="3"/>
       <c r="CB103" s="3"/>
-    </row>
-    <row r="104" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC103" s="3"/>
+      <c r="CD103" s="3"/>
+      <c r="CE103" s="3"/>
+      <c r="CF103" s="3"/>
+      <c r="CG103" s="3"/>
+      <c r="CH103" s="3"/>
+    </row>
+    <row r="104" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -8994,8 +9827,14 @@
       <c r="BZ104" s="3"/>
       <c r="CA104" s="3"/>
       <c r="CB104" s="3"/>
-    </row>
-    <row r="105" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC104" s="3"/>
+      <c r="CD104" s="3"/>
+      <c r="CE104" s="3"/>
+      <c r="CF104" s="3"/>
+      <c r="CG104" s="3"/>
+      <c r="CH104" s="3"/>
+    </row>
+    <row r="105" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -9074,8 +9913,14 @@
       <c r="BZ105" s="3"/>
       <c r="CA105" s="3"/>
       <c r="CB105" s="3"/>
-    </row>
-    <row r="106" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC105" s="3"/>
+      <c r="CD105" s="3"/>
+      <c r="CE105" s="3"/>
+      <c r="CF105" s="3"/>
+      <c r="CG105" s="3"/>
+      <c r="CH105" s="3"/>
+    </row>
+    <row r="106" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -9154,8 +9999,14 @@
       <c r="BZ106" s="3"/>
       <c r="CA106" s="3"/>
       <c r="CB106" s="3"/>
-    </row>
-    <row r="107" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC106" s="3"/>
+      <c r="CD106" s="3"/>
+      <c r="CE106" s="3"/>
+      <c r="CF106" s="3"/>
+      <c r="CG106" s="3"/>
+      <c r="CH106" s="3"/>
+    </row>
+    <row r="107" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -9234,8 +10085,14 @@
       <c r="BZ107" s="3"/>
       <c r="CA107" s="3"/>
       <c r="CB107" s="3"/>
-    </row>
-    <row r="108" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC107" s="3"/>
+      <c r="CD107" s="3"/>
+      <c r="CE107" s="3"/>
+      <c r="CF107" s="3"/>
+      <c r="CG107" s="3"/>
+      <c r="CH107" s="3"/>
+    </row>
+    <row r="108" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -9314,8 +10171,14 @@
       <c r="BZ108" s="3"/>
       <c r="CA108" s="3"/>
       <c r="CB108" s="3"/>
-    </row>
-    <row r="109" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC108" s="3"/>
+      <c r="CD108" s="3"/>
+      <c r="CE108" s="3"/>
+      <c r="CF108" s="3"/>
+      <c r="CG108" s="3"/>
+      <c r="CH108" s="3"/>
+    </row>
+    <row r="109" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -9394,8 +10257,14 @@
       <c r="BZ109" s="3"/>
       <c r="CA109" s="3"/>
       <c r="CB109" s="3"/>
-    </row>
-    <row r="110" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC109" s="3"/>
+      <c r="CD109" s="3"/>
+      <c r="CE109" s="3"/>
+      <c r="CF109" s="3"/>
+      <c r="CG109" s="3"/>
+      <c r="CH109" s="3"/>
+    </row>
+    <row r="110" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -9474,8 +10343,14 @@
       <c r="BZ110" s="3"/>
       <c r="CA110" s="3"/>
       <c r="CB110" s="3"/>
-    </row>
-    <row r="111" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC110" s="3"/>
+      <c r="CD110" s="3"/>
+      <c r="CE110" s="3"/>
+      <c r="CF110" s="3"/>
+      <c r="CG110" s="3"/>
+      <c r="CH110" s="3"/>
+    </row>
+    <row r="111" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -9554,8 +10429,14 @@
       <c r="BZ111" s="3"/>
       <c r="CA111" s="3"/>
       <c r="CB111" s="3"/>
-    </row>
-    <row r="112" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC111" s="3"/>
+      <c r="CD111" s="3"/>
+      <c r="CE111" s="3"/>
+      <c r="CF111" s="3"/>
+      <c r="CG111" s="3"/>
+      <c r="CH111" s="3"/>
+    </row>
+    <row r="112" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -9634,8 +10515,14 @@
       <c r="BZ112" s="3"/>
       <c r="CA112" s="3"/>
       <c r="CB112" s="3"/>
-    </row>
-    <row r="113" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC112" s="3"/>
+      <c r="CD112" s="3"/>
+      <c r="CE112" s="3"/>
+      <c r="CF112" s="3"/>
+      <c r="CG112" s="3"/>
+      <c r="CH112" s="3"/>
+    </row>
+    <row r="113" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -9714,8 +10601,14 @@
       <c r="BZ113" s="3"/>
       <c r="CA113" s="3"/>
       <c r="CB113" s="3"/>
-    </row>
-    <row r="114" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC113" s="3"/>
+      <c r="CD113" s="3"/>
+      <c r="CE113" s="3"/>
+      <c r="CF113" s="3"/>
+      <c r="CG113" s="3"/>
+      <c r="CH113" s="3"/>
+    </row>
+    <row r="114" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -9794,8 +10687,14 @@
       <c r="BZ114" s="3"/>
       <c r="CA114" s="3"/>
       <c r="CB114" s="3"/>
-    </row>
-    <row r="115" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC114" s="3"/>
+      <c r="CD114" s="3"/>
+      <c r="CE114" s="3"/>
+      <c r="CF114" s="3"/>
+      <c r="CG114" s="3"/>
+      <c r="CH114" s="3"/>
+    </row>
+    <row r="115" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -9874,8 +10773,14 @@
       <c r="BZ115" s="3"/>
       <c r="CA115" s="3"/>
       <c r="CB115" s="3"/>
-    </row>
-    <row r="116" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC115" s="3"/>
+      <c r="CD115" s="3"/>
+      <c r="CE115" s="3"/>
+      <c r="CF115" s="3"/>
+      <c r="CG115" s="3"/>
+      <c r="CH115" s="3"/>
+    </row>
+    <row r="116" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -9954,8 +10859,14 @@
       <c r="BZ116" s="3"/>
       <c r="CA116" s="3"/>
       <c r="CB116" s="3"/>
-    </row>
-    <row r="117" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC116" s="3"/>
+      <c r="CD116" s="3"/>
+      <c r="CE116" s="3"/>
+      <c r="CF116" s="3"/>
+      <c r="CG116" s="3"/>
+      <c r="CH116" s="3"/>
+    </row>
+    <row r="117" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -10034,8 +10945,14 @@
       <c r="BZ117" s="3"/>
       <c r="CA117" s="3"/>
       <c r="CB117" s="3"/>
-    </row>
-    <row r="118" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC117" s="3"/>
+      <c r="CD117" s="3"/>
+      <c r="CE117" s="3"/>
+      <c r="CF117" s="3"/>
+      <c r="CG117" s="3"/>
+      <c r="CH117" s="3"/>
+    </row>
+    <row r="118" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -10114,8 +11031,14 @@
       <c r="BZ118" s="3"/>
       <c r="CA118" s="3"/>
       <c r="CB118" s="3"/>
-    </row>
-    <row r="119" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC118" s="3"/>
+      <c r="CD118" s="3"/>
+      <c r="CE118" s="3"/>
+      <c r="CF118" s="3"/>
+      <c r="CG118" s="3"/>
+      <c r="CH118" s="3"/>
+    </row>
+    <row r="119" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -10194,8 +11117,14 @@
       <c r="BZ119" s="3"/>
       <c r="CA119" s="3"/>
       <c r="CB119" s="3"/>
-    </row>
-    <row r="120" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC119" s="3"/>
+      <c r="CD119" s="3"/>
+      <c r="CE119" s="3"/>
+      <c r="CF119" s="3"/>
+      <c r="CG119" s="3"/>
+      <c r="CH119" s="3"/>
+    </row>
+    <row r="120" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -10274,8 +11203,14 @@
       <c r="BZ120" s="3"/>
       <c r="CA120" s="3"/>
       <c r="CB120" s="3"/>
-    </row>
-    <row r="121" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC120" s="3"/>
+      <c r="CD120" s="3"/>
+      <c r="CE120" s="3"/>
+      <c r="CF120" s="3"/>
+      <c r="CG120" s="3"/>
+      <c r="CH120" s="3"/>
+    </row>
+    <row r="121" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -10354,8 +11289,14 @@
       <c r="BZ121" s="3"/>
       <c r="CA121" s="3"/>
       <c r="CB121" s="3"/>
-    </row>
-    <row r="122" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC121" s="3"/>
+      <c r="CD121" s="3"/>
+      <c r="CE121" s="3"/>
+      <c r="CF121" s="3"/>
+      <c r="CG121" s="3"/>
+      <c r="CH121" s="3"/>
+    </row>
+    <row r="122" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -10434,8 +11375,14 @@
       <c r="BZ122" s="3"/>
       <c r="CA122" s="3"/>
       <c r="CB122" s="3"/>
-    </row>
-    <row r="123" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC122" s="3"/>
+      <c r="CD122" s="3"/>
+      <c r="CE122" s="3"/>
+      <c r="CF122" s="3"/>
+      <c r="CG122" s="3"/>
+      <c r="CH122" s="3"/>
+    </row>
+    <row r="123" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -10514,8 +11461,14 @@
       <c r="BZ123" s="3"/>
       <c r="CA123" s="3"/>
       <c r="CB123" s="3"/>
-    </row>
-    <row r="124" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC123" s="3"/>
+      <c r="CD123" s="3"/>
+      <c r="CE123" s="3"/>
+      <c r="CF123" s="3"/>
+      <c r="CG123" s="3"/>
+      <c r="CH123" s="3"/>
+    </row>
+    <row r="124" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -10594,8 +11547,14 @@
       <c r="BZ124" s="3"/>
       <c r="CA124" s="3"/>
       <c r="CB124" s="3"/>
-    </row>
-    <row r="125" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC124" s="3"/>
+      <c r="CD124" s="3"/>
+      <c r="CE124" s="3"/>
+      <c r="CF124" s="3"/>
+      <c r="CG124" s="3"/>
+      <c r="CH124" s="3"/>
+    </row>
+    <row r="125" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -10674,8 +11633,14 @@
       <c r="BZ125" s="3"/>
       <c r="CA125" s="3"/>
       <c r="CB125" s="3"/>
-    </row>
-    <row r="126" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC125" s="3"/>
+      <c r="CD125" s="3"/>
+      <c r="CE125" s="3"/>
+      <c r="CF125" s="3"/>
+      <c r="CG125" s="3"/>
+      <c r="CH125" s="3"/>
+    </row>
+    <row r="126" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -10754,8 +11719,14 @@
       <c r="BZ126" s="3"/>
       <c r="CA126" s="3"/>
       <c r="CB126" s="3"/>
-    </row>
-    <row r="127" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC126" s="3"/>
+      <c r="CD126" s="3"/>
+      <c r="CE126" s="3"/>
+      <c r="CF126" s="3"/>
+      <c r="CG126" s="3"/>
+      <c r="CH126" s="3"/>
+    </row>
+    <row r="127" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -10834,8 +11805,14 @@
       <c r="BZ127" s="3"/>
       <c r="CA127" s="3"/>
       <c r="CB127" s="3"/>
-    </row>
-    <row r="128" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC127" s="3"/>
+      <c r="CD127" s="3"/>
+      <c r="CE127" s="3"/>
+      <c r="CF127" s="3"/>
+      <c r="CG127" s="3"/>
+      <c r="CH127" s="3"/>
+    </row>
+    <row r="128" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -10914,8 +11891,14 @@
       <c r="BZ128" s="3"/>
       <c r="CA128" s="3"/>
       <c r="CB128" s="3"/>
-    </row>
-    <row r="129" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC128" s="3"/>
+      <c r="CD128" s="3"/>
+      <c r="CE128" s="3"/>
+      <c r="CF128" s="3"/>
+      <c r="CG128" s="3"/>
+      <c r="CH128" s="3"/>
+    </row>
+    <row r="129" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -10994,8 +11977,14 @@
       <c r="BZ129" s="3"/>
       <c r="CA129" s="3"/>
       <c r="CB129" s="3"/>
-    </row>
-    <row r="130" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC129" s="3"/>
+      <c r="CD129" s="3"/>
+      <c r="CE129" s="3"/>
+      <c r="CF129" s="3"/>
+      <c r="CG129" s="3"/>
+      <c r="CH129" s="3"/>
+    </row>
+    <row r="130" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -11074,8 +12063,14 @@
       <c r="BZ130" s="3"/>
       <c r="CA130" s="3"/>
       <c r="CB130" s="3"/>
-    </row>
-    <row r="131" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC130" s="3"/>
+      <c r="CD130" s="3"/>
+      <c r="CE130" s="3"/>
+      <c r="CF130" s="3"/>
+      <c r="CG130" s="3"/>
+      <c r="CH130" s="3"/>
+    </row>
+    <row r="131" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -11154,8 +12149,14 @@
       <c r="BZ131" s="3"/>
       <c r="CA131" s="3"/>
       <c r="CB131" s="3"/>
-    </row>
-    <row r="132" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC131" s="3"/>
+      <c r="CD131" s="3"/>
+      <c r="CE131" s="3"/>
+      <c r="CF131" s="3"/>
+      <c r="CG131" s="3"/>
+      <c r="CH131" s="3"/>
+    </row>
+    <row r="132" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -11234,8 +12235,14 @@
       <c r="BZ132" s="3"/>
       <c r="CA132" s="3"/>
       <c r="CB132" s="3"/>
-    </row>
-    <row r="133" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC132" s="3"/>
+      <c r="CD132" s="3"/>
+      <c r="CE132" s="3"/>
+      <c r="CF132" s="3"/>
+      <c r="CG132" s="3"/>
+      <c r="CH132" s="3"/>
+    </row>
+    <row r="133" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -11314,8 +12321,14 @@
       <c r="BZ133" s="3"/>
       <c r="CA133" s="3"/>
       <c r="CB133" s="3"/>
-    </row>
-    <row r="134" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC133" s="3"/>
+      <c r="CD133" s="3"/>
+      <c r="CE133" s="3"/>
+      <c r="CF133" s="3"/>
+      <c r="CG133" s="3"/>
+      <c r="CH133" s="3"/>
+    </row>
+    <row r="134" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -11394,8 +12407,14 @@
       <c r="BZ134" s="3"/>
       <c r="CA134" s="3"/>
       <c r="CB134" s="3"/>
-    </row>
-    <row r="135" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC134" s="3"/>
+      <c r="CD134" s="3"/>
+      <c r="CE134" s="3"/>
+      <c r="CF134" s="3"/>
+      <c r="CG134" s="3"/>
+      <c r="CH134" s="3"/>
+    </row>
+    <row r="135" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -11474,8 +12493,14 @@
       <c r="BZ135" s="3"/>
       <c r="CA135" s="3"/>
       <c r="CB135" s="3"/>
-    </row>
-    <row r="136" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC135" s="3"/>
+      <c r="CD135" s="3"/>
+      <c r="CE135" s="3"/>
+      <c r="CF135" s="3"/>
+      <c r="CG135" s="3"/>
+      <c r="CH135" s="3"/>
+    </row>
+    <row r="136" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -11554,8 +12579,14 @@
       <c r="BZ136" s="3"/>
       <c r="CA136" s="3"/>
       <c r="CB136" s="3"/>
-    </row>
-    <row r="137" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC136" s="3"/>
+      <c r="CD136" s="3"/>
+      <c r="CE136" s="3"/>
+      <c r="CF136" s="3"/>
+      <c r="CG136" s="3"/>
+      <c r="CH136" s="3"/>
+    </row>
+    <row r="137" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -11634,8 +12665,14 @@
       <c r="BZ137" s="3"/>
       <c r="CA137" s="3"/>
       <c r="CB137" s="3"/>
-    </row>
-    <row r="138" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC137" s="3"/>
+      <c r="CD137" s="3"/>
+      <c r="CE137" s="3"/>
+      <c r="CF137" s="3"/>
+      <c r="CG137" s="3"/>
+      <c r="CH137" s="3"/>
+    </row>
+    <row r="138" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -11714,8 +12751,14 @@
       <c r="BZ138" s="3"/>
       <c r="CA138" s="3"/>
       <c r="CB138" s="3"/>
-    </row>
-    <row r="139" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC138" s="3"/>
+      <c r="CD138" s="3"/>
+      <c r="CE138" s="3"/>
+      <c r="CF138" s="3"/>
+      <c r="CG138" s="3"/>
+      <c r="CH138" s="3"/>
+    </row>
+    <row r="139" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -11794,8 +12837,14 @@
       <c r="BZ139" s="3"/>
       <c r="CA139" s="3"/>
       <c r="CB139" s="3"/>
-    </row>
-    <row r="140" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC139" s="3"/>
+      <c r="CD139" s="3"/>
+      <c r="CE139" s="3"/>
+      <c r="CF139" s="3"/>
+      <c r="CG139" s="3"/>
+      <c r="CH139" s="3"/>
+    </row>
+    <row r="140" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -11874,8 +12923,14 @@
       <c r="BZ140" s="3"/>
       <c r="CA140" s="3"/>
       <c r="CB140" s="3"/>
-    </row>
-    <row r="141" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC140" s="3"/>
+      <c r="CD140" s="3"/>
+      <c r="CE140" s="3"/>
+      <c r="CF140" s="3"/>
+      <c r="CG140" s="3"/>
+      <c r="CH140" s="3"/>
+    </row>
+    <row r="141" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -11954,8 +13009,14 @@
       <c r="BZ141" s="3"/>
       <c r="CA141" s="3"/>
       <c r="CB141" s="3"/>
-    </row>
-    <row r="142" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC141" s="3"/>
+      <c r="CD141" s="3"/>
+      <c r="CE141" s="3"/>
+      <c r="CF141" s="3"/>
+      <c r="CG141" s="3"/>
+      <c r="CH141" s="3"/>
+    </row>
+    <row r="142" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -12034,8 +13095,14 @@
       <c r="BZ142" s="3"/>
       <c r="CA142" s="3"/>
       <c r="CB142" s="3"/>
-    </row>
-    <row r="143" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC142" s="3"/>
+      <c r="CD142" s="3"/>
+      <c r="CE142" s="3"/>
+      <c r="CF142" s="3"/>
+      <c r="CG142" s="3"/>
+      <c r="CH142" s="3"/>
+    </row>
+    <row r="143" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -12114,8 +13181,14 @@
       <c r="BZ143" s="3"/>
       <c r="CA143" s="3"/>
       <c r="CB143" s="3"/>
-    </row>
-    <row r="144" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC143" s="3"/>
+      <c r="CD143" s="3"/>
+      <c r="CE143" s="3"/>
+      <c r="CF143" s="3"/>
+      <c r="CG143" s="3"/>
+      <c r="CH143" s="3"/>
+    </row>
+    <row r="144" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -12194,8 +13267,14 @@
       <c r="BZ144" s="3"/>
       <c r="CA144" s="3"/>
       <c r="CB144" s="3"/>
-    </row>
-    <row r="145" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC144" s="3"/>
+      <c r="CD144" s="3"/>
+      <c r="CE144" s="3"/>
+      <c r="CF144" s="3"/>
+      <c r="CG144" s="3"/>
+      <c r="CH144" s="3"/>
+    </row>
+    <row r="145" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -12274,8 +13353,14 @@
       <c r="BZ145" s="3"/>
       <c r="CA145" s="3"/>
       <c r="CB145" s="3"/>
-    </row>
-    <row r="146" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC145" s="3"/>
+      <c r="CD145" s="3"/>
+      <c r="CE145" s="3"/>
+      <c r="CF145" s="3"/>
+      <c r="CG145" s="3"/>
+      <c r="CH145" s="3"/>
+    </row>
+    <row r="146" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -12354,8 +13439,14 @@
       <c r="BZ146" s="3"/>
       <c r="CA146" s="3"/>
       <c r="CB146" s="3"/>
-    </row>
-    <row r="147" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC146" s="3"/>
+      <c r="CD146" s="3"/>
+      <c r="CE146" s="3"/>
+      <c r="CF146" s="3"/>
+      <c r="CG146" s="3"/>
+      <c r="CH146" s="3"/>
+    </row>
+    <row r="147" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -12434,8 +13525,14 @@
       <c r="BZ147" s="3"/>
       <c r="CA147" s="3"/>
       <c r="CB147" s="3"/>
-    </row>
-    <row r="148" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC147" s="3"/>
+      <c r="CD147" s="3"/>
+      <c r="CE147" s="3"/>
+      <c r="CF147" s="3"/>
+      <c r="CG147" s="3"/>
+      <c r="CH147" s="3"/>
+    </row>
+    <row r="148" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -12514,8 +13611,14 @@
       <c r="BZ148" s="3"/>
       <c r="CA148" s="3"/>
       <c r="CB148" s="3"/>
-    </row>
-    <row r="149" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC148" s="3"/>
+      <c r="CD148" s="3"/>
+      <c r="CE148" s="3"/>
+      <c r="CF148" s="3"/>
+      <c r="CG148" s="3"/>
+      <c r="CH148" s="3"/>
+    </row>
+    <row r="149" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -12594,8 +13697,14 @@
       <c r="BZ149" s="3"/>
       <c r="CA149" s="3"/>
       <c r="CB149" s="3"/>
-    </row>
-    <row r="150" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC149" s="3"/>
+      <c r="CD149" s="3"/>
+      <c r="CE149" s="3"/>
+      <c r="CF149" s="3"/>
+      <c r="CG149" s="3"/>
+      <c r="CH149" s="3"/>
+    </row>
+    <row r="150" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -12674,8 +13783,14 @@
       <c r="BZ150" s="3"/>
       <c r="CA150" s="3"/>
       <c r="CB150" s="3"/>
-    </row>
-    <row r="151" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC150" s="3"/>
+      <c r="CD150" s="3"/>
+      <c r="CE150" s="3"/>
+      <c r="CF150" s="3"/>
+      <c r="CG150" s="3"/>
+      <c r="CH150" s="3"/>
+    </row>
+    <row r="151" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -12754,8 +13869,14 @@
       <c r="BZ151" s="3"/>
       <c r="CA151" s="3"/>
       <c r="CB151" s="3"/>
-    </row>
-    <row r="152" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC151" s="3"/>
+      <c r="CD151" s="3"/>
+      <c r="CE151" s="3"/>
+      <c r="CF151" s="3"/>
+      <c r="CG151" s="3"/>
+      <c r="CH151" s="3"/>
+    </row>
+    <row r="152" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -12834,8 +13955,14 @@
       <c r="BZ152" s="3"/>
       <c r="CA152" s="3"/>
       <c r="CB152" s="3"/>
-    </row>
-    <row r="153" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC152" s="3"/>
+      <c r="CD152" s="3"/>
+      <c r="CE152" s="3"/>
+      <c r="CF152" s="3"/>
+      <c r="CG152" s="3"/>
+      <c r="CH152" s="3"/>
+    </row>
+    <row r="153" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -12914,8 +14041,14 @@
       <c r="BZ153" s="3"/>
       <c r="CA153" s="3"/>
       <c r="CB153" s="3"/>
-    </row>
-    <row r="154" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC153" s="3"/>
+      <c r="CD153" s="3"/>
+      <c r="CE153" s="3"/>
+      <c r="CF153" s="3"/>
+      <c r="CG153" s="3"/>
+      <c r="CH153" s="3"/>
+    </row>
+    <row r="154" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -12994,8 +14127,14 @@
       <c r="BZ154" s="3"/>
       <c r="CA154" s="3"/>
       <c r="CB154" s="3"/>
-    </row>
-    <row r="155" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC154" s="3"/>
+      <c r="CD154" s="3"/>
+      <c r="CE154" s="3"/>
+      <c r="CF154" s="3"/>
+      <c r="CG154" s="3"/>
+      <c r="CH154" s="3"/>
+    </row>
+    <row r="155" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -13074,8 +14213,14 @@
       <c r="BZ155" s="3"/>
       <c r="CA155" s="3"/>
       <c r="CB155" s="3"/>
-    </row>
-    <row r="156" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC155" s="3"/>
+      <c r="CD155" s="3"/>
+      <c r="CE155" s="3"/>
+      <c r="CF155" s="3"/>
+      <c r="CG155" s="3"/>
+      <c r="CH155" s="3"/>
+    </row>
+    <row r="156" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -13154,8 +14299,14 @@
       <c r="BZ156" s="3"/>
       <c r="CA156" s="3"/>
       <c r="CB156" s="3"/>
-    </row>
-    <row r="157" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC156" s="3"/>
+      <c r="CD156" s="3"/>
+      <c r="CE156" s="3"/>
+      <c r="CF156" s="3"/>
+      <c r="CG156" s="3"/>
+      <c r="CH156" s="3"/>
+    </row>
+    <row r="157" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -13234,8 +14385,14 @@
       <c r="BZ157" s="3"/>
       <c r="CA157" s="3"/>
       <c r="CB157" s="3"/>
-    </row>
-    <row r="158" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC157" s="3"/>
+      <c r="CD157" s="3"/>
+      <c r="CE157" s="3"/>
+      <c r="CF157" s="3"/>
+      <c r="CG157" s="3"/>
+      <c r="CH157" s="3"/>
+    </row>
+    <row r="158" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -13314,8 +14471,14 @@
       <c r="BZ158" s="3"/>
       <c r="CA158" s="3"/>
       <c r="CB158" s="3"/>
-    </row>
-    <row r="159" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC158" s="3"/>
+      <c r="CD158" s="3"/>
+      <c r="CE158" s="3"/>
+      <c r="CF158" s="3"/>
+      <c r="CG158" s="3"/>
+      <c r="CH158" s="3"/>
+    </row>
+    <row r="159" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -13394,8 +14557,14 @@
       <c r="BZ159" s="3"/>
       <c r="CA159" s="3"/>
       <c r="CB159" s="3"/>
-    </row>
-    <row r="160" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC159" s="3"/>
+      <c r="CD159" s="3"/>
+      <c r="CE159" s="3"/>
+      <c r="CF159" s="3"/>
+      <c r="CG159" s="3"/>
+      <c r="CH159" s="3"/>
+    </row>
+    <row r="160" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -13474,8 +14643,14 @@
       <c r="BZ160" s="3"/>
       <c r="CA160" s="3"/>
       <c r="CB160" s="3"/>
-    </row>
-    <row r="161" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC160" s="3"/>
+      <c r="CD160" s="3"/>
+      <c r="CE160" s="3"/>
+      <c r="CF160" s="3"/>
+      <c r="CG160" s="3"/>
+      <c r="CH160" s="3"/>
+    </row>
+    <row r="161" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -13554,8 +14729,14 @@
       <c r="BZ161" s="3"/>
       <c r="CA161" s="3"/>
       <c r="CB161" s="3"/>
-    </row>
-    <row r="162" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC161" s="3"/>
+      <c r="CD161" s="3"/>
+      <c r="CE161" s="3"/>
+      <c r="CF161" s="3"/>
+      <c r="CG161" s="3"/>
+      <c r="CH161" s="3"/>
+    </row>
+    <row r="162" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -13634,8 +14815,14 @@
       <c r="BZ162" s="3"/>
       <c r="CA162" s="3"/>
       <c r="CB162" s="3"/>
-    </row>
-    <row r="163" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC162" s="3"/>
+      <c r="CD162" s="3"/>
+      <c r="CE162" s="3"/>
+      <c r="CF162" s="3"/>
+      <c r="CG162" s="3"/>
+      <c r="CH162" s="3"/>
+    </row>
+    <row r="163" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -13714,8 +14901,14 @@
       <c r="BZ163" s="3"/>
       <c r="CA163" s="3"/>
       <c r="CB163" s="3"/>
-    </row>
-    <row r="164" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC163" s="3"/>
+      <c r="CD163" s="3"/>
+      <c r="CE163" s="3"/>
+      <c r="CF163" s="3"/>
+      <c r="CG163" s="3"/>
+      <c r="CH163" s="3"/>
+    </row>
+    <row r="164" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -13794,8 +14987,14 @@
       <c r="BZ164" s="3"/>
       <c r="CA164" s="3"/>
       <c r="CB164" s="3"/>
-    </row>
-    <row r="165" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC164" s="3"/>
+      <c r="CD164" s="3"/>
+      <c r="CE164" s="3"/>
+      <c r="CF164" s="3"/>
+      <c r="CG164" s="3"/>
+      <c r="CH164" s="3"/>
+    </row>
+    <row r="165" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -13874,8 +15073,14 @@
       <c r="BZ165" s="3"/>
       <c r="CA165" s="3"/>
       <c r="CB165" s="3"/>
-    </row>
-    <row r="166" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC165" s="3"/>
+      <c r="CD165" s="3"/>
+      <c r="CE165" s="3"/>
+      <c r="CF165" s="3"/>
+      <c r="CG165" s="3"/>
+      <c r="CH165" s="3"/>
+    </row>
+    <row r="166" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -13954,8 +15159,14 @@
       <c r="BZ166" s="3"/>
       <c r="CA166" s="3"/>
       <c r="CB166" s="3"/>
-    </row>
-    <row r="167" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC166" s="3"/>
+      <c r="CD166" s="3"/>
+      <c r="CE166" s="3"/>
+      <c r="CF166" s="3"/>
+      <c r="CG166" s="3"/>
+      <c r="CH166" s="3"/>
+    </row>
+    <row r="167" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -14034,8 +15245,14 @@
       <c r="BZ167" s="3"/>
       <c r="CA167" s="3"/>
       <c r="CB167" s="3"/>
-    </row>
-    <row r="168" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC167" s="3"/>
+      <c r="CD167" s="3"/>
+      <c r="CE167" s="3"/>
+      <c r="CF167" s="3"/>
+      <c r="CG167" s="3"/>
+      <c r="CH167" s="3"/>
+    </row>
+    <row r="168" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -14114,8 +15331,14 @@
       <c r="BZ168" s="3"/>
       <c r="CA168" s="3"/>
       <c r="CB168" s="3"/>
-    </row>
-    <row r="169" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC168" s="3"/>
+      <c r="CD168" s="3"/>
+      <c r="CE168" s="3"/>
+      <c r="CF168" s="3"/>
+      <c r="CG168" s="3"/>
+      <c r="CH168" s="3"/>
+    </row>
+    <row r="169" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -14194,8 +15417,14 @@
       <c r="BZ169" s="3"/>
       <c r="CA169" s="3"/>
       <c r="CB169" s="3"/>
-    </row>
-    <row r="170" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC169" s="3"/>
+      <c r="CD169" s="3"/>
+      <c r="CE169" s="3"/>
+      <c r="CF169" s="3"/>
+      <c r="CG169" s="3"/>
+      <c r="CH169" s="3"/>
+    </row>
+    <row r="170" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -14274,8 +15503,14 @@
       <c r="BZ170" s="3"/>
       <c r="CA170" s="3"/>
       <c r="CB170" s="3"/>
-    </row>
-    <row r="171" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC170" s="3"/>
+      <c r="CD170" s="3"/>
+      <c r="CE170" s="3"/>
+      <c r="CF170" s="3"/>
+      <c r="CG170" s="3"/>
+      <c r="CH170" s="3"/>
+    </row>
+    <row r="171" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -14354,8 +15589,14 @@
       <c r="BZ171" s="3"/>
       <c r="CA171" s="3"/>
       <c r="CB171" s="3"/>
-    </row>
-    <row r="172" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC171" s="3"/>
+      <c r="CD171" s="3"/>
+      <c r="CE171" s="3"/>
+      <c r="CF171" s="3"/>
+      <c r="CG171" s="3"/>
+      <c r="CH171" s="3"/>
+    </row>
+    <row r="172" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -14434,8 +15675,14 @@
       <c r="BZ172" s="3"/>
       <c r="CA172" s="3"/>
       <c r="CB172" s="3"/>
-    </row>
-    <row r="173" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC172" s="3"/>
+      <c r="CD172" s="3"/>
+      <c r="CE172" s="3"/>
+      <c r="CF172" s="3"/>
+      <c r="CG172" s="3"/>
+      <c r="CH172" s="3"/>
+    </row>
+    <row r="173" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -14514,8 +15761,14 @@
       <c r="BZ173" s="3"/>
       <c r="CA173" s="3"/>
       <c r="CB173" s="3"/>
-    </row>
-    <row r="174" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC173" s="3"/>
+      <c r="CD173" s="3"/>
+      <c r="CE173" s="3"/>
+      <c r="CF173" s="3"/>
+      <c r="CG173" s="3"/>
+      <c r="CH173" s="3"/>
+    </row>
+    <row r="174" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -14594,8 +15847,14 @@
       <c r="BZ174" s="3"/>
       <c r="CA174" s="3"/>
       <c r="CB174" s="3"/>
-    </row>
-    <row r="175" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC174" s="3"/>
+      <c r="CD174" s="3"/>
+      <c r="CE174" s="3"/>
+      <c r="CF174" s="3"/>
+      <c r="CG174" s="3"/>
+      <c r="CH174" s="3"/>
+    </row>
+    <row r="175" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -14674,8 +15933,14 @@
       <c r="BZ175" s="3"/>
       <c r="CA175" s="3"/>
       <c r="CB175" s="3"/>
-    </row>
-    <row r="176" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC175" s="3"/>
+      <c r="CD175" s="3"/>
+      <c r="CE175" s="3"/>
+      <c r="CF175" s="3"/>
+      <c r="CG175" s="3"/>
+      <c r="CH175" s="3"/>
+    </row>
+    <row r="176" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -14754,8 +16019,14 @@
       <c r="BZ176" s="3"/>
       <c r="CA176" s="3"/>
       <c r="CB176" s="3"/>
-    </row>
-    <row r="177" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC176" s="3"/>
+      <c r="CD176" s="3"/>
+      <c r="CE176" s="3"/>
+      <c r="CF176" s="3"/>
+      <c r="CG176" s="3"/>
+      <c r="CH176" s="3"/>
+    </row>
+    <row r="177" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -14834,8 +16105,14 @@
       <c r="BZ177" s="3"/>
       <c r="CA177" s="3"/>
       <c r="CB177" s="3"/>
-    </row>
-    <row r="178" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC177" s="3"/>
+      <c r="CD177" s="3"/>
+      <c r="CE177" s="3"/>
+      <c r="CF177" s="3"/>
+      <c r="CG177" s="3"/>
+      <c r="CH177" s="3"/>
+    </row>
+    <row r="178" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -14914,8 +16191,14 @@
       <c r="BZ178" s="3"/>
       <c r="CA178" s="3"/>
       <c r="CB178" s="3"/>
-    </row>
-    <row r="179" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC178" s="3"/>
+      <c r="CD178" s="3"/>
+      <c r="CE178" s="3"/>
+      <c r="CF178" s="3"/>
+      <c r="CG178" s="3"/>
+      <c r="CH178" s="3"/>
+    </row>
+    <row r="179" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -14994,8 +16277,14 @@
       <c r="BZ179" s="3"/>
       <c r="CA179" s="3"/>
       <c r="CB179" s="3"/>
-    </row>
-    <row r="180" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC179" s="3"/>
+      <c r="CD179" s="3"/>
+      <c r="CE179" s="3"/>
+      <c r="CF179" s="3"/>
+      <c r="CG179" s="3"/>
+      <c r="CH179" s="3"/>
+    </row>
+    <row r="180" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -15074,8 +16363,14 @@
       <c r="BZ180" s="3"/>
       <c r="CA180" s="3"/>
       <c r="CB180" s="3"/>
-    </row>
-    <row r="181" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC180" s="3"/>
+      <c r="CD180" s="3"/>
+      <c r="CE180" s="3"/>
+      <c r="CF180" s="3"/>
+      <c r="CG180" s="3"/>
+      <c r="CH180" s="3"/>
+    </row>
+    <row r="181" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -15154,8 +16449,14 @@
       <c r="BZ181" s="3"/>
       <c r="CA181" s="3"/>
       <c r="CB181" s="3"/>
-    </row>
-    <row r="182" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC181" s="3"/>
+      <c r="CD181" s="3"/>
+      <c r="CE181" s="3"/>
+      <c r="CF181" s="3"/>
+      <c r="CG181" s="3"/>
+      <c r="CH181" s="3"/>
+    </row>
+    <row r="182" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -15234,8 +16535,14 @@
       <c r="BZ182" s="3"/>
       <c r="CA182" s="3"/>
       <c r="CB182" s="3"/>
-    </row>
-    <row r="183" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC182" s="3"/>
+      <c r="CD182" s="3"/>
+      <c r="CE182" s="3"/>
+      <c r="CF182" s="3"/>
+      <c r="CG182" s="3"/>
+      <c r="CH182" s="3"/>
+    </row>
+    <row r="183" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -15314,8 +16621,14 @@
       <c r="BZ183" s="3"/>
       <c r="CA183" s="3"/>
       <c r="CB183" s="3"/>
-    </row>
-    <row r="184" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC183" s="3"/>
+      <c r="CD183" s="3"/>
+      <c r="CE183" s="3"/>
+      <c r="CF183" s="3"/>
+      <c r="CG183" s="3"/>
+      <c r="CH183" s="3"/>
+    </row>
+    <row r="184" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -15394,8 +16707,14 @@
       <c r="BZ184" s="3"/>
       <c r="CA184" s="3"/>
       <c r="CB184" s="3"/>
-    </row>
-    <row r="185" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC184" s="3"/>
+      <c r="CD184" s="3"/>
+      <c r="CE184" s="3"/>
+      <c r="CF184" s="3"/>
+      <c r="CG184" s="3"/>
+      <c r="CH184" s="3"/>
+    </row>
+    <row r="185" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -15474,8 +16793,14 @@
       <c r="BZ185" s="3"/>
       <c r="CA185" s="3"/>
       <c r="CB185" s="3"/>
-    </row>
-    <row r="186" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC185" s="3"/>
+      <c r="CD185" s="3"/>
+      <c r="CE185" s="3"/>
+      <c r="CF185" s="3"/>
+      <c r="CG185" s="3"/>
+      <c r="CH185" s="3"/>
+    </row>
+    <row r="186" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -15554,8 +16879,14 @@
       <c r="BZ186" s="3"/>
       <c r="CA186" s="3"/>
       <c r="CB186" s="3"/>
-    </row>
-    <row r="187" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC186" s="3"/>
+      <c r="CD186" s="3"/>
+      <c r="CE186" s="3"/>
+      <c r="CF186" s="3"/>
+      <c r="CG186" s="3"/>
+      <c r="CH186" s="3"/>
+    </row>
+    <row r="187" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -15634,8 +16965,14 @@
       <c r="BZ187" s="3"/>
       <c r="CA187" s="3"/>
       <c r="CB187" s="3"/>
-    </row>
-    <row r="188" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC187" s="3"/>
+      <c r="CD187" s="3"/>
+      <c r="CE187" s="3"/>
+      <c r="CF187" s="3"/>
+      <c r="CG187" s="3"/>
+      <c r="CH187" s="3"/>
+    </row>
+    <row r="188" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -15714,8 +17051,14 @@
       <c r="BZ188" s="3"/>
       <c r="CA188" s="3"/>
       <c r="CB188" s="3"/>
-    </row>
-    <row r="189" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC188" s="3"/>
+      <c r="CD188" s="3"/>
+      <c r="CE188" s="3"/>
+      <c r="CF188" s="3"/>
+      <c r="CG188" s="3"/>
+      <c r="CH188" s="3"/>
+    </row>
+    <row r="189" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -15794,8 +17137,14 @@
       <c r="BZ189" s="3"/>
       <c r="CA189" s="3"/>
       <c r="CB189" s="3"/>
-    </row>
-    <row r="190" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC189" s="3"/>
+      <c r="CD189" s="3"/>
+      <c r="CE189" s="3"/>
+      <c r="CF189" s="3"/>
+      <c r="CG189" s="3"/>
+      <c r="CH189" s="3"/>
+    </row>
+    <row r="190" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -15874,8 +17223,14 @@
       <c r="BZ190" s="3"/>
       <c r="CA190" s="3"/>
       <c r="CB190" s="3"/>
-    </row>
-    <row r="191" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC190" s="3"/>
+      <c r="CD190" s="3"/>
+      <c r="CE190" s="3"/>
+      <c r="CF190" s="3"/>
+      <c r="CG190" s="3"/>
+      <c r="CH190" s="3"/>
+    </row>
+    <row r="191" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -15954,8 +17309,14 @@
       <c r="BZ191" s="3"/>
       <c r="CA191" s="3"/>
       <c r="CB191" s="3"/>
-    </row>
-    <row r="192" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC191" s="3"/>
+      <c r="CD191" s="3"/>
+      <c r="CE191" s="3"/>
+      <c r="CF191" s="3"/>
+      <c r="CG191" s="3"/>
+      <c r="CH191" s="3"/>
+    </row>
+    <row r="192" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -16034,8 +17395,14 @@
       <c r="BZ192" s="3"/>
       <c r="CA192" s="3"/>
       <c r="CB192" s="3"/>
-    </row>
-    <row r="193" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC192" s="3"/>
+      <c r="CD192" s="3"/>
+      <c r="CE192" s="3"/>
+      <c r="CF192" s="3"/>
+      <c r="CG192" s="3"/>
+      <c r="CH192" s="3"/>
+    </row>
+    <row r="193" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -16114,8 +17481,14 @@
       <c r="BZ193" s="3"/>
       <c r="CA193" s="3"/>
       <c r="CB193" s="3"/>
-    </row>
-    <row r="194" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC193" s="3"/>
+      <c r="CD193" s="3"/>
+      <c r="CE193" s="3"/>
+      <c r="CF193" s="3"/>
+      <c r="CG193" s="3"/>
+      <c r="CH193" s="3"/>
+    </row>
+    <row r="194" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -16194,8 +17567,14 @@
       <c r="BZ194" s="3"/>
       <c r="CA194" s="3"/>
       <c r="CB194" s="3"/>
-    </row>
-    <row r="195" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC194" s="3"/>
+      <c r="CD194" s="3"/>
+      <c r="CE194" s="3"/>
+      <c r="CF194" s="3"/>
+      <c r="CG194" s="3"/>
+      <c r="CH194" s="3"/>
+    </row>
+    <row r="195" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -16274,8 +17653,14 @@
       <c r="BZ195" s="3"/>
       <c r="CA195" s="3"/>
       <c r="CB195" s="3"/>
-    </row>
-    <row r="196" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC195" s="3"/>
+      <c r="CD195" s="3"/>
+      <c r="CE195" s="3"/>
+      <c r="CF195" s="3"/>
+      <c r="CG195" s="3"/>
+      <c r="CH195" s="3"/>
+    </row>
+    <row r="196" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -16354,8 +17739,14 @@
       <c r="BZ196" s="3"/>
       <c r="CA196" s="3"/>
       <c r="CB196" s="3"/>
-    </row>
-    <row r="197" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC196" s="3"/>
+      <c r="CD196" s="3"/>
+      <c r="CE196" s="3"/>
+      <c r="CF196" s="3"/>
+      <c r="CG196" s="3"/>
+      <c r="CH196" s="3"/>
+    </row>
+    <row r="197" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -16434,8 +17825,14 @@
       <c r="BZ197" s="3"/>
       <c r="CA197" s="3"/>
       <c r="CB197" s="3"/>
-    </row>
-    <row r="198" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC197" s="3"/>
+      <c r="CD197" s="3"/>
+      <c r="CE197" s="3"/>
+      <c r="CF197" s="3"/>
+      <c r="CG197" s="3"/>
+      <c r="CH197" s="3"/>
+    </row>
+    <row r="198" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -16514,8 +17911,14 @@
       <c r="BZ198" s="3"/>
       <c r="CA198" s="3"/>
       <c r="CB198" s="3"/>
-    </row>
-    <row r="199" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC198" s="3"/>
+      <c r="CD198" s="3"/>
+      <c r="CE198" s="3"/>
+      <c r="CF198" s="3"/>
+      <c r="CG198" s="3"/>
+      <c r="CH198" s="3"/>
+    </row>
+    <row r="199" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -16594,8 +17997,14 @@
       <c r="BZ199" s="3"/>
       <c r="CA199" s="3"/>
       <c r="CB199" s="3"/>
-    </row>
-    <row r="200" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC199" s="3"/>
+      <c r="CD199" s="3"/>
+      <c r="CE199" s="3"/>
+      <c r="CF199" s="3"/>
+      <c r="CG199" s="3"/>
+      <c r="CH199" s="3"/>
+    </row>
+    <row r="200" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -16674,8 +18083,14 @@
       <c r="BZ200" s="3"/>
       <c r="CA200" s="3"/>
       <c r="CB200" s="3"/>
-    </row>
-    <row r="201" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC200" s="3"/>
+      <c r="CD200" s="3"/>
+      <c r="CE200" s="3"/>
+      <c r="CF200" s="3"/>
+      <c r="CG200" s="3"/>
+      <c r="CH200" s="3"/>
+    </row>
+    <row r="201" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -16754,8 +18169,14 @@
       <c r="BZ201" s="3"/>
       <c r="CA201" s="3"/>
       <c r="CB201" s="3"/>
-    </row>
-    <row r="202" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC201" s="3"/>
+      <c r="CD201" s="3"/>
+      <c r="CE201" s="3"/>
+      <c r="CF201" s="3"/>
+      <c r="CG201" s="3"/>
+      <c r="CH201" s="3"/>
+    </row>
+    <row r="202" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -16834,8 +18255,14 @@
       <c r="BZ202" s="3"/>
       <c r="CA202" s="3"/>
       <c r="CB202" s="3"/>
-    </row>
-    <row r="203" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC202" s="3"/>
+      <c r="CD202" s="3"/>
+      <c r="CE202" s="3"/>
+      <c r="CF202" s="3"/>
+      <c r="CG202" s="3"/>
+      <c r="CH202" s="3"/>
+    </row>
+    <row r="203" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -16914,8 +18341,14 @@
       <c r="BZ203" s="3"/>
       <c r="CA203" s="3"/>
       <c r="CB203" s="3"/>
-    </row>
-    <row r="204" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC203" s="3"/>
+      <c r="CD203" s="3"/>
+      <c r="CE203" s="3"/>
+      <c r="CF203" s="3"/>
+      <c r="CG203" s="3"/>
+      <c r="CH203" s="3"/>
+    </row>
+    <row r="204" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -16994,8 +18427,14 @@
       <c r="BZ204" s="3"/>
       <c r="CA204" s="3"/>
       <c r="CB204" s="3"/>
-    </row>
-    <row r="205" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC204" s="3"/>
+      <c r="CD204" s="3"/>
+      <c r="CE204" s="3"/>
+      <c r="CF204" s="3"/>
+      <c r="CG204" s="3"/>
+      <c r="CH204" s="3"/>
+    </row>
+    <row r="205" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -17074,8 +18513,14 @@
       <c r="BZ205" s="3"/>
       <c r="CA205" s="3"/>
       <c r="CB205" s="3"/>
-    </row>
-    <row r="206" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC205" s="3"/>
+      <c r="CD205" s="3"/>
+      <c r="CE205" s="3"/>
+      <c r="CF205" s="3"/>
+      <c r="CG205" s="3"/>
+      <c r="CH205" s="3"/>
+    </row>
+    <row r="206" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -17154,8 +18599,14 @@
       <c r="BZ206" s="3"/>
       <c r="CA206" s="3"/>
       <c r="CB206" s="3"/>
-    </row>
-    <row r="207" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC206" s="3"/>
+      <c r="CD206" s="3"/>
+      <c r="CE206" s="3"/>
+      <c r="CF206" s="3"/>
+      <c r="CG206" s="3"/>
+      <c r="CH206" s="3"/>
+    </row>
+    <row r="207" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -17234,8 +18685,14 @@
       <c r="BZ207" s="3"/>
       <c r="CA207" s="3"/>
       <c r="CB207" s="3"/>
-    </row>
-    <row r="208" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC207" s="3"/>
+      <c r="CD207" s="3"/>
+      <c r="CE207" s="3"/>
+      <c r="CF207" s="3"/>
+      <c r="CG207" s="3"/>
+      <c r="CH207" s="3"/>
+    </row>
+    <row r="208" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -17314,8 +18771,14 @@
       <c r="BZ208" s="3"/>
       <c r="CA208" s="3"/>
       <c r="CB208" s="3"/>
-    </row>
-    <row r="209" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC208" s="3"/>
+      <c r="CD208" s="3"/>
+      <c r="CE208" s="3"/>
+      <c r="CF208" s="3"/>
+      <c r="CG208" s="3"/>
+      <c r="CH208" s="3"/>
+    </row>
+    <row r="209" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -17394,8 +18857,14 @@
       <c r="BZ209" s="3"/>
       <c r="CA209" s="3"/>
       <c r="CB209" s="3"/>
-    </row>
-    <row r="210" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC209" s="3"/>
+      <c r="CD209" s="3"/>
+      <c r="CE209" s="3"/>
+      <c r="CF209" s="3"/>
+      <c r="CG209" s="3"/>
+      <c r="CH209" s="3"/>
+    </row>
+    <row r="210" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -17474,8 +18943,14 @@
       <c r="BZ210" s="3"/>
       <c r="CA210" s="3"/>
       <c r="CB210" s="3"/>
-    </row>
-    <row r="211" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC210" s="3"/>
+      <c r="CD210" s="3"/>
+      <c r="CE210" s="3"/>
+      <c r="CF210" s="3"/>
+      <c r="CG210" s="3"/>
+      <c r="CH210" s="3"/>
+    </row>
+    <row r="211" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -17554,8 +19029,14 @@
       <c r="BZ211" s="3"/>
       <c r="CA211" s="3"/>
       <c r="CB211" s="3"/>
-    </row>
-    <row r="212" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC211" s="3"/>
+      <c r="CD211" s="3"/>
+      <c r="CE211" s="3"/>
+      <c r="CF211" s="3"/>
+      <c r="CG211" s="3"/>
+      <c r="CH211" s="3"/>
+    </row>
+    <row r="212" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -17634,8 +19115,14 @@
       <c r="BZ212" s="3"/>
       <c r="CA212" s="3"/>
       <c r="CB212" s="3"/>
-    </row>
-    <row r="213" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC212" s="3"/>
+      <c r="CD212" s="3"/>
+      <c r="CE212" s="3"/>
+      <c r="CF212" s="3"/>
+      <c r="CG212" s="3"/>
+      <c r="CH212" s="3"/>
+    </row>
+    <row r="213" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -17714,8 +19201,14 @@
       <c r="BZ213" s="3"/>
       <c r="CA213" s="3"/>
       <c r="CB213" s="3"/>
-    </row>
-    <row r="214" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC213" s="3"/>
+      <c r="CD213" s="3"/>
+      <c r="CE213" s="3"/>
+      <c r="CF213" s="3"/>
+      <c r="CG213" s="3"/>
+      <c r="CH213" s="3"/>
+    </row>
+    <row r="214" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -17794,8 +19287,14 @@
       <c r="BZ214" s="3"/>
       <c r="CA214" s="3"/>
       <c r="CB214" s="3"/>
-    </row>
-    <row r="215" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC214" s="3"/>
+      <c r="CD214" s="3"/>
+      <c r="CE214" s="3"/>
+      <c r="CF214" s="3"/>
+      <c r="CG214" s="3"/>
+      <c r="CH214" s="3"/>
+    </row>
+    <row r="215" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -17874,8 +19373,14 @@
       <c r="BZ215" s="3"/>
       <c r="CA215" s="3"/>
       <c r="CB215" s="3"/>
-    </row>
-    <row r="216" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC215" s="3"/>
+      <c r="CD215" s="3"/>
+      <c r="CE215" s="3"/>
+      <c r="CF215" s="3"/>
+      <c r="CG215" s="3"/>
+      <c r="CH215" s="3"/>
+    </row>
+    <row r="216" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -17954,8 +19459,14 @@
       <c r="BZ216" s="3"/>
       <c r="CA216" s="3"/>
       <c r="CB216" s="3"/>
-    </row>
-    <row r="217" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC216" s="3"/>
+      <c r="CD216" s="3"/>
+      <c r="CE216" s="3"/>
+      <c r="CF216" s="3"/>
+      <c r="CG216" s="3"/>
+      <c r="CH216" s="3"/>
+    </row>
+    <row r="217" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -18034,8 +19545,14 @@
       <c r="BZ217" s="3"/>
       <c r="CA217" s="3"/>
       <c r="CB217" s="3"/>
-    </row>
-    <row r="218" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC217" s="3"/>
+      <c r="CD217" s="3"/>
+      <c r="CE217" s="3"/>
+      <c r="CF217" s="3"/>
+      <c r="CG217" s="3"/>
+      <c r="CH217" s="3"/>
+    </row>
+    <row r="218" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -18114,8 +19631,14 @@
       <c r="BZ218" s="3"/>
       <c r="CA218" s="3"/>
       <c r="CB218" s="3"/>
-    </row>
-    <row r="219" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC218" s="3"/>
+      <c r="CD218" s="3"/>
+      <c r="CE218" s="3"/>
+      <c r="CF218" s="3"/>
+      <c r="CG218" s="3"/>
+      <c r="CH218" s="3"/>
+    </row>
+    <row r="219" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -18194,8 +19717,14 @@
       <c r="BZ219" s="3"/>
       <c r="CA219" s="3"/>
       <c r="CB219" s="3"/>
-    </row>
-    <row r="220" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC219" s="3"/>
+      <c r="CD219" s="3"/>
+      <c r="CE219" s="3"/>
+      <c r="CF219" s="3"/>
+      <c r="CG219" s="3"/>
+      <c r="CH219" s="3"/>
+    </row>
+    <row r="220" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -18274,8 +19803,14 @@
       <c r="BZ220" s="3"/>
       <c r="CA220" s="3"/>
       <c r="CB220" s="3"/>
-    </row>
-    <row r="221" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC220" s="3"/>
+      <c r="CD220" s="3"/>
+      <c r="CE220" s="3"/>
+      <c r="CF220" s="3"/>
+      <c r="CG220" s="3"/>
+      <c r="CH220" s="3"/>
+    </row>
+    <row r="221" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -18354,8 +19889,14 @@
       <c r="BZ221" s="3"/>
       <c r="CA221" s="3"/>
       <c r="CB221" s="3"/>
-    </row>
-    <row r="222" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC221" s="3"/>
+      <c r="CD221" s="3"/>
+      <c r="CE221" s="3"/>
+      <c r="CF221" s="3"/>
+      <c r="CG221" s="3"/>
+      <c r="CH221" s="3"/>
+    </row>
+    <row r="222" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -18434,8 +19975,14 @@
       <c r="BZ222" s="3"/>
       <c r="CA222" s="3"/>
       <c r="CB222" s="3"/>
-    </row>
-    <row r="223" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC222" s="3"/>
+      <c r="CD222" s="3"/>
+      <c r="CE222" s="3"/>
+      <c r="CF222" s="3"/>
+      <c r="CG222" s="3"/>
+      <c r="CH222" s="3"/>
+    </row>
+    <row r="223" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -18514,8 +20061,14 @@
       <c r="BZ223" s="3"/>
       <c r="CA223" s="3"/>
       <c r="CB223" s="3"/>
-    </row>
-    <row r="224" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC223" s="3"/>
+      <c r="CD223" s="3"/>
+      <c r="CE223" s="3"/>
+      <c r="CF223" s="3"/>
+      <c r="CG223" s="3"/>
+      <c r="CH223" s="3"/>
+    </row>
+    <row r="224" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -18594,8 +20147,14 @@
       <c r="BZ224" s="3"/>
       <c r="CA224" s="3"/>
       <c r="CB224" s="3"/>
-    </row>
-    <row r="225" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC224" s="3"/>
+      <c r="CD224" s="3"/>
+      <c r="CE224" s="3"/>
+      <c r="CF224" s="3"/>
+      <c r="CG224" s="3"/>
+      <c r="CH224" s="3"/>
+    </row>
+    <row r="225" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -18674,8 +20233,14 @@
       <c r="BZ225" s="3"/>
       <c r="CA225" s="3"/>
       <c r="CB225" s="3"/>
-    </row>
-    <row r="226" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC225" s="3"/>
+      <c r="CD225" s="3"/>
+      <c r="CE225" s="3"/>
+      <c r="CF225" s="3"/>
+      <c r="CG225" s="3"/>
+      <c r="CH225" s="3"/>
+    </row>
+    <row r="226" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -18754,8 +20319,14 @@
       <c r="BZ226" s="3"/>
       <c r="CA226" s="3"/>
       <c r="CB226" s="3"/>
-    </row>
-    <row r="227" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC226" s="3"/>
+      <c r="CD226" s="3"/>
+      <c r="CE226" s="3"/>
+      <c r="CF226" s="3"/>
+      <c r="CG226" s="3"/>
+      <c r="CH226" s="3"/>
+    </row>
+    <row r="227" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -18834,8 +20405,14 @@
       <c r="BZ227" s="3"/>
       <c r="CA227" s="3"/>
       <c r="CB227" s="3"/>
-    </row>
-    <row r="228" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC227" s="3"/>
+      <c r="CD227" s="3"/>
+      <c r="CE227" s="3"/>
+      <c r="CF227" s="3"/>
+      <c r="CG227" s="3"/>
+      <c r="CH227" s="3"/>
+    </row>
+    <row r="228" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -18914,8 +20491,14 @@
       <c r="BZ228" s="3"/>
       <c r="CA228" s="3"/>
       <c r="CB228" s="3"/>
-    </row>
-    <row r="229" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC228" s="3"/>
+      <c r="CD228" s="3"/>
+      <c r="CE228" s="3"/>
+      <c r="CF228" s="3"/>
+      <c r="CG228" s="3"/>
+      <c r="CH228" s="3"/>
+    </row>
+    <row r="229" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -18994,8 +20577,14 @@
       <c r="BZ229" s="3"/>
       <c r="CA229" s="3"/>
       <c r="CB229" s="3"/>
-    </row>
-    <row r="230" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC229" s="3"/>
+      <c r="CD229" s="3"/>
+      <c r="CE229" s="3"/>
+      <c r="CF229" s="3"/>
+      <c r="CG229" s="3"/>
+      <c r="CH229" s="3"/>
+    </row>
+    <row r="230" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -19074,8 +20663,14 @@
       <c r="BZ230" s="3"/>
       <c r="CA230" s="3"/>
       <c r="CB230" s="3"/>
-    </row>
-    <row r="231" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC230" s="3"/>
+      <c r="CD230" s="3"/>
+      <c r="CE230" s="3"/>
+      <c r="CF230" s="3"/>
+      <c r="CG230" s="3"/>
+      <c r="CH230" s="3"/>
+    </row>
+    <row r="231" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -19154,8 +20749,14 @@
       <c r="BZ231" s="3"/>
       <c r="CA231" s="3"/>
       <c r="CB231" s="3"/>
-    </row>
-    <row r="232" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC231" s="3"/>
+      <c r="CD231" s="3"/>
+      <c r="CE231" s="3"/>
+      <c r="CF231" s="3"/>
+      <c r="CG231" s="3"/>
+      <c r="CH231" s="3"/>
+    </row>
+    <row r="232" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -19234,8 +20835,14 @@
       <c r="BZ232" s="3"/>
       <c r="CA232" s="3"/>
       <c r="CB232" s="3"/>
-    </row>
-    <row r="233" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC232" s="3"/>
+      <c r="CD232" s="3"/>
+      <c r="CE232" s="3"/>
+      <c r="CF232" s="3"/>
+      <c r="CG232" s="3"/>
+      <c r="CH232" s="3"/>
+    </row>
+    <row r="233" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -19314,8 +20921,14 @@
       <c r="BZ233" s="3"/>
       <c r="CA233" s="3"/>
       <c r="CB233" s="3"/>
-    </row>
-    <row r="234" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC233" s="3"/>
+      <c r="CD233" s="3"/>
+      <c r="CE233" s="3"/>
+      <c r="CF233" s="3"/>
+      <c r="CG233" s="3"/>
+      <c r="CH233" s="3"/>
+    </row>
+    <row r="234" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -19394,8 +21007,14 @@
       <c r="BZ234" s="3"/>
       <c r="CA234" s="3"/>
       <c r="CB234" s="3"/>
-    </row>
-    <row r="235" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC234" s="3"/>
+      <c r="CD234" s="3"/>
+      <c r="CE234" s="3"/>
+      <c r="CF234" s="3"/>
+      <c r="CG234" s="3"/>
+      <c r="CH234" s="3"/>
+    </row>
+    <row r="235" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -19474,8 +21093,14 @@
       <c r="BZ235" s="3"/>
       <c r="CA235" s="3"/>
       <c r="CB235" s="3"/>
-    </row>
-    <row r="236" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC235" s="3"/>
+      <c r="CD235" s="3"/>
+      <c r="CE235" s="3"/>
+      <c r="CF235" s="3"/>
+      <c r="CG235" s="3"/>
+      <c r="CH235" s="3"/>
+    </row>
+    <row r="236" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -19554,8 +21179,14 @@
       <c r="BZ236" s="3"/>
       <c r="CA236" s="3"/>
       <c r="CB236" s="3"/>
-    </row>
-    <row r="237" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC236" s="3"/>
+      <c r="CD236" s="3"/>
+      <c r="CE236" s="3"/>
+      <c r="CF236" s="3"/>
+      <c r="CG236" s="3"/>
+      <c r="CH236" s="3"/>
+    </row>
+    <row r="237" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -19634,8 +21265,14 @@
       <c r="BZ237" s="3"/>
       <c r="CA237" s="3"/>
       <c r="CB237" s="3"/>
-    </row>
-    <row r="238" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC237" s="3"/>
+      <c r="CD237" s="3"/>
+      <c r="CE237" s="3"/>
+      <c r="CF237" s="3"/>
+      <c r="CG237" s="3"/>
+      <c r="CH237" s="3"/>
+    </row>
+    <row r="238" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -19714,8 +21351,14 @@
       <c r="BZ238" s="3"/>
       <c r="CA238" s="3"/>
       <c r="CB238" s="3"/>
-    </row>
-    <row r="239" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC238" s="3"/>
+      <c r="CD238" s="3"/>
+      <c r="CE238" s="3"/>
+      <c r="CF238" s="3"/>
+      <c r="CG238" s="3"/>
+      <c r="CH238" s="3"/>
+    </row>
+    <row r="239" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -19794,8 +21437,14 @@
       <c r="BZ239" s="3"/>
       <c r="CA239" s="3"/>
       <c r="CB239" s="3"/>
-    </row>
-    <row r="240" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC239" s="3"/>
+      <c r="CD239" s="3"/>
+      <c r="CE239" s="3"/>
+      <c r="CF239" s="3"/>
+      <c r="CG239" s="3"/>
+      <c r="CH239" s="3"/>
+    </row>
+    <row r="240" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -19874,8 +21523,14 @@
       <c r="BZ240" s="3"/>
       <c r="CA240" s="3"/>
       <c r="CB240" s="3"/>
-    </row>
-    <row r="241" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC240" s="3"/>
+      <c r="CD240" s="3"/>
+      <c r="CE240" s="3"/>
+      <c r="CF240" s="3"/>
+      <c r="CG240" s="3"/>
+      <c r="CH240" s="3"/>
+    </row>
+    <row r="241" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -19954,8 +21609,14 @@
       <c r="BZ241" s="3"/>
       <c r="CA241" s="3"/>
       <c r="CB241" s="3"/>
-    </row>
-    <row r="242" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC241" s="3"/>
+      <c r="CD241" s="3"/>
+      <c r="CE241" s="3"/>
+      <c r="CF241" s="3"/>
+      <c r="CG241" s="3"/>
+      <c r="CH241" s="3"/>
+    </row>
+    <row r="242" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -20034,8 +21695,14 @@
       <c r="BZ242" s="3"/>
       <c r="CA242" s="3"/>
       <c r="CB242" s="3"/>
-    </row>
-    <row r="243" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC242" s="3"/>
+      <c r="CD242" s="3"/>
+      <c r="CE242" s="3"/>
+      <c r="CF242" s="3"/>
+      <c r="CG242" s="3"/>
+      <c r="CH242" s="3"/>
+    </row>
+    <row r="243" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -20114,8 +21781,14 @@
       <c r="BZ243" s="3"/>
       <c r="CA243" s="3"/>
       <c r="CB243" s="3"/>
-    </row>
-    <row r="244" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC243" s="3"/>
+      <c r="CD243" s="3"/>
+      <c r="CE243" s="3"/>
+      <c r="CF243" s="3"/>
+      <c r="CG243" s="3"/>
+      <c r="CH243" s="3"/>
+    </row>
+    <row r="244" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -20194,8 +21867,14 @@
       <c r="BZ244" s="3"/>
       <c r="CA244" s="3"/>
       <c r="CB244" s="3"/>
-    </row>
-    <row r="245" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC244" s="3"/>
+      <c r="CD244" s="3"/>
+      <c r="CE244" s="3"/>
+      <c r="CF244" s="3"/>
+      <c r="CG244" s="3"/>
+      <c r="CH244" s="3"/>
+    </row>
+    <row r="245" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -20274,8 +21953,14 @@
       <c r="BZ245" s="3"/>
       <c r="CA245" s="3"/>
       <c r="CB245" s="3"/>
-    </row>
-    <row r="246" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC245" s="3"/>
+      <c r="CD245" s="3"/>
+      <c r="CE245" s="3"/>
+      <c r="CF245" s="3"/>
+      <c r="CG245" s="3"/>
+      <c r="CH245" s="3"/>
+    </row>
+    <row r="246" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -20354,8 +22039,14 @@
       <c r="BZ246" s="3"/>
       <c r="CA246" s="3"/>
       <c r="CB246" s="3"/>
-    </row>
-    <row r="247" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC246" s="3"/>
+      <c r="CD246" s="3"/>
+      <c r="CE246" s="3"/>
+      <c r="CF246" s="3"/>
+      <c r="CG246" s="3"/>
+      <c r="CH246" s="3"/>
+    </row>
+    <row r="247" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -20434,8 +22125,14 @@
       <c r="BZ247" s="3"/>
       <c r="CA247" s="3"/>
       <c r="CB247" s="3"/>
-    </row>
-    <row r="248" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC247" s="3"/>
+      <c r="CD247" s="3"/>
+      <c r="CE247" s="3"/>
+      <c r="CF247" s="3"/>
+      <c r="CG247" s="3"/>
+      <c r="CH247" s="3"/>
+    </row>
+    <row r="248" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -20514,8 +22211,14 @@
       <c r="BZ248" s="3"/>
       <c r="CA248" s="3"/>
       <c r="CB248" s="3"/>
-    </row>
-    <row r="249" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC248" s="3"/>
+      <c r="CD248" s="3"/>
+      <c r="CE248" s="3"/>
+      <c r="CF248" s="3"/>
+      <c r="CG248" s="3"/>
+      <c r="CH248" s="3"/>
+    </row>
+    <row r="249" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -20594,8 +22297,14 @@
       <c r="BZ249" s="3"/>
       <c r="CA249" s="3"/>
       <c r="CB249" s="3"/>
-    </row>
-    <row r="250" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC249" s="3"/>
+      <c r="CD249" s="3"/>
+      <c r="CE249" s="3"/>
+      <c r="CF249" s="3"/>
+      <c r="CG249" s="3"/>
+      <c r="CH249" s="3"/>
+    </row>
+    <row r="250" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -20674,8 +22383,14 @@
       <c r="BZ250" s="3"/>
       <c r="CA250" s="3"/>
       <c r="CB250" s="3"/>
-    </row>
-    <row r="251" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC250" s="3"/>
+      <c r="CD250" s="3"/>
+      <c r="CE250" s="3"/>
+      <c r="CF250" s="3"/>
+      <c r="CG250" s="3"/>
+      <c r="CH250" s="3"/>
+    </row>
+    <row r="251" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -20754,8 +22469,14 @@
       <c r="BZ251" s="3"/>
       <c r="CA251" s="3"/>
       <c r="CB251" s="3"/>
-    </row>
-    <row r="252" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC251" s="3"/>
+      <c r="CD251" s="3"/>
+      <c r="CE251" s="3"/>
+      <c r="CF251" s="3"/>
+      <c r="CG251" s="3"/>
+      <c r="CH251" s="3"/>
+    </row>
+    <row r="252" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -20834,8 +22555,14 @@
       <c r="BZ252" s="3"/>
       <c r="CA252" s="3"/>
       <c r="CB252" s="3"/>
-    </row>
-    <row r="253" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC252" s="3"/>
+      <c r="CD252" s="3"/>
+      <c r="CE252" s="3"/>
+      <c r="CF252" s="3"/>
+      <c r="CG252" s="3"/>
+      <c r="CH252" s="3"/>
+    </row>
+    <row r="253" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -20914,8 +22641,14 @@
       <c r="BZ253" s="3"/>
       <c r="CA253" s="3"/>
       <c r="CB253" s="3"/>
-    </row>
-    <row r="254" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC253" s="3"/>
+      <c r="CD253" s="3"/>
+      <c r="CE253" s="3"/>
+      <c r="CF253" s="3"/>
+      <c r="CG253" s="3"/>
+      <c r="CH253" s="3"/>
+    </row>
+    <row r="254" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -20994,8 +22727,14 @@
       <c r="BZ254" s="3"/>
       <c r="CA254" s="3"/>
       <c r="CB254" s="3"/>
-    </row>
-    <row r="255" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC254" s="3"/>
+      <c r="CD254" s="3"/>
+      <c r="CE254" s="3"/>
+      <c r="CF254" s="3"/>
+      <c r="CG254" s="3"/>
+      <c r="CH254" s="3"/>
+    </row>
+    <row r="255" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -21074,8 +22813,14 @@
       <c r="BZ255" s="3"/>
       <c r="CA255" s="3"/>
       <c r="CB255" s="3"/>
-    </row>
-    <row r="256" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC255" s="3"/>
+      <c r="CD255" s="3"/>
+      <c r="CE255" s="3"/>
+      <c r="CF255" s="3"/>
+      <c r="CG255" s="3"/>
+      <c r="CH255" s="3"/>
+    </row>
+    <row r="256" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -21154,8 +22899,14 @@
       <c r="BZ256" s="3"/>
       <c r="CA256" s="3"/>
       <c r="CB256" s="3"/>
-    </row>
-    <row r="257" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC256" s="3"/>
+      <c r="CD256" s="3"/>
+      <c r="CE256" s="3"/>
+      <c r="CF256" s="3"/>
+      <c r="CG256" s="3"/>
+      <c r="CH256" s="3"/>
+    </row>
+    <row r="257" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -21234,8 +22985,14 @@
       <c r="BZ257" s="3"/>
       <c r="CA257" s="3"/>
       <c r="CB257" s="3"/>
-    </row>
-    <row r="258" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC257" s="3"/>
+      <c r="CD257" s="3"/>
+      <c r="CE257" s="3"/>
+      <c r="CF257" s="3"/>
+      <c r="CG257" s="3"/>
+      <c r="CH257" s="3"/>
+    </row>
+    <row r="258" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -21314,8 +23071,14 @@
       <c r="BZ258" s="3"/>
       <c r="CA258" s="3"/>
       <c r="CB258" s="3"/>
-    </row>
-    <row r="259" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC258" s="3"/>
+      <c r="CD258" s="3"/>
+      <c r="CE258" s="3"/>
+      <c r="CF258" s="3"/>
+      <c r="CG258" s="3"/>
+      <c r="CH258" s="3"/>
+    </row>
+    <row r="259" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -21394,8 +23157,14 @@
       <c r="BZ259" s="3"/>
       <c r="CA259" s="3"/>
       <c r="CB259" s="3"/>
-    </row>
-    <row r="260" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC259" s="3"/>
+      <c r="CD259" s="3"/>
+      <c r="CE259" s="3"/>
+      <c r="CF259" s="3"/>
+      <c r="CG259" s="3"/>
+      <c r="CH259" s="3"/>
+    </row>
+    <row r="260" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -21474,8 +23243,14 @@
       <c r="BZ260" s="3"/>
       <c r="CA260" s="3"/>
       <c r="CB260" s="3"/>
-    </row>
-    <row r="261" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC260" s="3"/>
+      <c r="CD260" s="3"/>
+      <c r="CE260" s="3"/>
+      <c r="CF260" s="3"/>
+      <c r="CG260" s="3"/>
+      <c r="CH260" s="3"/>
+    </row>
+    <row r="261" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -21554,8 +23329,14 @@
       <c r="BZ261" s="3"/>
       <c r="CA261" s="3"/>
       <c r="CB261" s="3"/>
-    </row>
-    <row r="262" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC261" s="3"/>
+      <c r="CD261" s="3"/>
+      <c r="CE261" s="3"/>
+      <c r="CF261" s="3"/>
+      <c r="CG261" s="3"/>
+      <c r="CH261" s="3"/>
+    </row>
+    <row r="262" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -21634,8 +23415,14 @@
       <c r="BZ262" s="3"/>
       <c r="CA262" s="3"/>
       <c r="CB262" s="3"/>
-    </row>
-    <row r="263" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC262" s="3"/>
+      <c r="CD262" s="3"/>
+      <c r="CE262" s="3"/>
+      <c r="CF262" s="3"/>
+      <c r="CG262" s="3"/>
+      <c r="CH262" s="3"/>
+    </row>
+    <row r="263" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -21714,8 +23501,14 @@
       <c r="BZ263" s="3"/>
       <c r="CA263" s="3"/>
       <c r="CB263" s="3"/>
-    </row>
-    <row r="264" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC263" s="3"/>
+      <c r="CD263" s="3"/>
+      <c r="CE263" s="3"/>
+      <c r="CF263" s="3"/>
+      <c r="CG263" s="3"/>
+      <c r="CH263" s="3"/>
+    </row>
+    <row r="264" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -21794,8 +23587,14 @@
       <c r="BZ264" s="3"/>
       <c r="CA264" s="3"/>
       <c r="CB264" s="3"/>
-    </row>
-    <row r="265" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC264" s="3"/>
+      <c r="CD264" s="3"/>
+      <c r="CE264" s="3"/>
+      <c r="CF264" s="3"/>
+      <c r="CG264" s="3"/>
+      <c r="CH264" s="3"/>
+    </row>
+    <row r="265" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -21874,8 +23673,14 @@
       <c r="BZ265" s="3"/>
       <c r="CA265" s="3"/>
       <c r="CB265" s="3"/>
-    </row>
-    <row r="266" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC265" s="3"/>
+      <c r="CD265" s="3"/>
+      <c r="CE265" s="3"/>
+      <c r="CF265" s="3"/>
+      <c r="CG265" s="3"/>
+      <c r="CH265" s="3"/>
+    </row>
+    <row r="266" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -21954,8 +23759,14 @@
       <c r="BZ266" s="3"/>
       <c r="CA266" s="3"/>
       <c r="CB266" s="3"/>
-    </row>
-    <row r="267" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC266" s="3"/>
+      <c r="CD266" s="3"/>
+      <c r="CE266" s="3"/>
+      <c r="CF266" s="3"/>
+      <c r="CG266" s="3"/>
+      <c r="CH266" s="3"/>
+    </row>
+    <row r="267" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -22034,8 +23845,14 @@
       <c r="BZ267" s="3"/>
       <c r="CA267" s="3"/>
       <c r="CB267" s="3"/>
-    </row>
-    <row r="268" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC267" s="3"/>
+      <c r="CD267" s="3"/>
+      <c r="CE267" s="3"/>
+      <c r="CF267" s="3"/>
+      <c r="CG267" s="3"/>
+      <c r="CH267" s="3"/>
+    </row>
+    <row r="268" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -22114,8 +23931,14 @@
       <c r="BZ268" s="3"/>
       <c r="CA268" s="3"/>
       <c r="CB268" s="3"/>
-    </row>
-    <row r="269" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC268" s="3"/>
+      <c r="CD268" s="3"/>
+      <c r="CE268" s="3"/>
+      <c r="CF268" s="3"/>
+      <c r="CG268" s="3"/>
+      <c r="CH268" s="3"/>
+    </row>
+    <row r="269" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -22194,8 +24017,14 @@
       <c r="BZ269" s="3"/>
       <c r="CA269" s="3"/>
       <c r="CB269" s="3"/>
-    </row>
-    <row r="270" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC269" s="3"/>
+      <c r="CD269" s="3"/>
+      <c r="CE269" s="3"/>
+      <c r="CF269" s="3"/>
+      <c r="CG269" s="3"/>
+      <c r="CH269" s="3"/>
+    </row>
+    <row r="270" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -22274,8 +24103,14 @@
       <c r="BZ270" s="3"/>
       <c r="CA270" s="3"/>
       <c r="CB270" s="3"/>
-    </row>
-    <row r="271" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC270" s="3"/>
+      <c r="CD270" s="3"/>
+      <c r="CE270" s="3"/>
+      <c r="CF270" s="3"/>
+      <c r="CG270" s="3"/>
+      <c r="CH270" s="3"/>
+    </row>
+    <row r="271" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -22354,8 +24189,14 @@
       <c r="BZ271" s="3"/>
       <c r="CA271" s="3"/>
       <c r="CB271" s="3"/>
-    </row>
-    <row r="272" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC271" s="3"/>
+      <c r="CD271" s="3"/>
+      <c r="CE271" s="3"/>
+      <c r="CF271" s="3"/>
+      <c r="CG271" s="3"/>
+      <c r="CH271" s="3"/>
+    </row>
+    <row r="272" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -22434,8 +24275,14 @@
       <c r="BZ272" s="3"/>
       <c r="CA272" s="3"/>
       <c r="CB272" s="3"/>
-    </row>
-    <row r="273" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC272" s="3"/>
+      <c r="CD272" s="3"/>
+      <c r="CE272" s="3"/>
+      <c r="CF272" s="3"/>
+      <c r="CG272" s="3"/>
+      <c r="CH272" s="3"/>
+    </row>
+    <row r="273" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -22514,8 +24361,14 @@
       <c r="BZ273" s="3"/>
       <c r="CA273" s="3"/>
       <c r="CB273" s="3"/>
-    </row>
-    <row r="274" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC273" s="3"/>
+      <c r="CD273" s="3"/>
+      <c r="CE273" s="3"/>
+      <c r="CF273" s="3"/>
+      <c r="CG273" s="3"/>
+      <c r="CH273" s="3"/>
+    </row>
+    <row r="274" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -22594,8 +24447,14 @@
       <c r="BZ274" s="3"/>
       <c r="CA274" s="3"/>
       <c r="CB274" s="3"/>
-    </row>
-    <row r="275" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC274" s="3"/>
+      <c r="CD274" s="3"/>
+      <c r="CE274" s="3"/>
+      <c r="CF274" s="3"/>
+      <c r="CG274" s="3"/>
+      <c r="CH274" s="3"/>
+    </row>
+    <row r="275" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -22674,8 +24533,14 @@
       <c r="BZ275" s="3"/>
       <c r="CA275" s="3"/>
       <c r="CB275" s="3"/>
-    </row>
-    <row r="276" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC275" s="3"/>
+      <c r="CD275" s="3"/>
+      <c r="CE275" s="3"/>
+      <c r="CF275" s="3"/>
+      <c r="CG275" s="3"/>
+      <c r="CH275" s="3"/>
+    </row>
+    <row r="276" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -22754,8 +24619,14 @@
       <c r="BZ276" s="3"/>
       <c r="CA276" s="3"/>
       <c r="CB276" s="3"/>
-    </row>
-    <row r="277" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC276" s="3"/>
+      <c r="CD276" s="3"/>
+      <c r="CE276" s="3"/>
+      <c r="CF276" s="3"/>
+      <c r="CG276" s="3"/>
+      <c r="CH276" s="3"/>
+    </row>
+    <row r="277" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -22834,8 +24705,14 @@
       <c r="BZ277" s="3"/>
       <c r="CA277" s="3"/>
       <c r="CB277" s="3"/>
-    </row>
-    <row r="278" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC277" s="3"/>
+      <c r="CD277" s="3"/>
+      <c r="CE277" s="3"/>
+      <c r="CF277" s="3"/>
+      <c r="CG277" s="3"/>
+      <c r="CH277" s="3"/>
+    </row>
+    <row r="278" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -22914,8 +24791,14 @@
       <c r="BZ278" s="3"/>
       <c r="CA278" s="3"/>
       <c r="CB278" s="3"/>
-    </row>
-    <row r="279" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC278" s="3"/>
+      <c r="CD278" s="3"/>
+      <c r="CE278" s="3"/>
+      <c r="CF278" s="3"/>
+      <c r="CG278" s="3"/>
+      <c r="CH278" s="3"/>
+    </row>
+    <row r="279" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -22994,8 +24877,14 @@
       <c r="BZ279" s="3"/>
       <c r="CA279" s="3"/>
       <c r="CB279" s="3"/>
-    </row>
-    <row r="280" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC279" s="3"/>
+      <c r="CD279" s="3"/>
+      <c r="CE279" s="3"/>
+      <c r="CF279" s="3"/>
+      <c r="CG279" s="3"/>
+      <c r="CH279" s="3"/>
+    </row>
+    <row r="280" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -23074,8 +24963,14 @@
       <c r="BZ280" s="3"/>
       <c r="CA280" s="3"/>
       <c r="CB280" s="3"/>
-    </row>
-    <row r="281" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC280" s="3"/>
+      <c r="CD280" s="3"/>
+      <c r="CE280" s="3"/>
+      <c r="CF280" s="3"/>
+      <c r="CG280" s="3"/>
+      <c r="CH280" s="3"/>
+    </row>
+    <row r="281" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -23154,8 +25049,14 @@
       <c r="BZ281" s="3"/>
       <c r="CA281" s="3"/>
       <c r="CB281" s="3"/>
-    </row>
-    <row r="282" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC281" s="3"/>
+      <c r="CD281" s="3"/>
+      <c r="CE281" s="3"/>
+      <c r="CF281" s="3"/>
+      <c r="CG281" s="3"/>
+      <c r="CH281" s="3"/>
+    </row>
+    <row r="282" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -23234,8 +25135,14 @@
       <c r="BZ282" s="3"/>
       <c r="CA282" s="3"/>
       <c r="CB282" s="3"/>
-    </row>
-    <row r="283" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC282" s="3"/>
+      <c r="CD282" s="3"/>
+      <c r="CE282" s="3"/>
+      <c r="CF282" s="3"/>
+      <c r="CG282" s="3"/>
+      <c r="CH282" s="3"/>
+    </row>
+    <row r="283" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -23314,8 +25221,14 @@
       <c r="BZ283" s="3"/>
       <c r="CA283" s="3"/>
       <c r="CB283" s="3"/>
-    </row>
-    <row r="284" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC283" s="3"/>
+      <c r="CD283" s="3"/>
+      <c r="CE283" s="3"/>
+      <c r="CF283" s="3"/>
+      <c r="CG283" s="3"/>
+      <c r="CH283" s="3"/>
+    </row>
+    <row r="284" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -23394,8 +25307,14 @@
       <c r="BZ284" s="3"/>
       <c r="CA284" s="3"/>
       <c r="CB284" s="3"/>
-    </row>
-    <row r="285" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC284" s="3"/>
+      <c r="CD284" s="3"/>
+      <c r="CE284" s="3"/>
+      <c r="CF284" s="3"/>
+      <c r="CG284" s="3"/>
+      <c r="CH284" s="3"/>
+    </row>
+    <row r="285" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -23474,8 +25393,14 @@
       <c r="BZ285" s="3"/>
       <c r="CA285" s="3"/>
       <c r="CB285" s="3"/>
-    </row>
-    <row r="286" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC285" s="3"/>
+      <c r="CD285" s="3"/>
+      <c r="CE285" s="3"/>
+      <c r="CF285" s="3"/>
+      <c r="CG285" s="3"/>
+      <c r="CH285" s="3"/>
+    </row>
+    <row r="286" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -23554,8 +25479,14 @@
       <c r="BZ286" s="3"/>
       <c r="CA286" s="3"/>
       <c r="CB286" s="3"/>
-    </row>
-    <row r="287" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC286" s="3"/>
+      <c r="CD286" s="3"/>
+      <c r="CE286" s="3"/>
+      <c r="CF286" s="3"/>
+      <c r="CG286" s="3"/>
+      <c r="CH286" s="3"/>
+    </row>
+    <row r="287" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -23634,8 +25565,14 @@
       <c r="BZ287" s="3"/>
       <c r="CA287" s="3"/>
       <c r="CB287" s="3"/>
-    </row>
-    <row r="288" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC287" s="3"/>
+      <c r="CD287" s="3"/>
+      <c r="CE287" s="3"/>
+      <c r="CF287" s="3"/>
+      <c r="CG287" s="3"/>
+      <c r="CH287" s="3"/>
+    </row>
+    <row r="288" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -23714,8 +25651,14 @@
       <c r="BZ288" s="3"/>
       <c r="CA288" s="3"/>
       <c r="CB288" s="3"/>
-    </row>
-    <row r="289" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC288" s="3"/>
+      <c r="CD288" s="3"/>
+      <c r="CE288" s="3"/>
+      <c r="CF288" s="3"/>
+      <c r="CG288" s="3"/>
+      <c r="CH288" s="3"/>
+    </row>
+    <row r="289" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -23794,8 +25737,14 @@
       <c r="BZ289" s="3"/>
       <c r="CA289" s="3"/>
       <c r="CB289" s="3"/>
-    </row>
-    <row r="290" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC289" s="3"/>
+      <c r="CD289" s="3"/>
+      <c r="CE289" s="3"/>
+      <c r="CF289" s="3"/>
+      <c r="CG289" s="3"/>
+      <c r="CH289" s="3"/>
+    </row>
+    <row r="290" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -23874,8 +25823,14 @@
       <c r="BZ290" s="3"/>
       <c r="CA290" s="3"/>
       <c r="CB290" s="3"/>
-    </row>
-    <row r="291" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC290" s="3"/>
+      <c r="CD290" s="3"/>
+      <c r="CE290" s="3"/>
+      <c r="CF290" s="3"/>
+      <c r="CG290" s="3"/>
+      <c r="CH290" s="3"/>
+    </row>
+    <row r="291" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -23954,8 +25909,14 @@
       <c r="BZ291" s="3"/>
       <c r="CA291" s="3"/>
       <c r="CB291" s="3"/>
-    </row>
-    <row r="292" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC291" s="3"/>
+      <c r="CD291" s="3"/>
+      <c r="CE291" s="3"/>
+      <c r="CF291" s="3"/>
+      <c r="CG291" s="3"/>
+      <c r="CH291" s="3"/>
+    </row>
+    <row r="292" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -24034,8 +25995,14 @@
       <c r="BZ292" s="3"/>
       <c r="CA292" s="3"/>
       <c r="CB292" s="3"/>
-    </row>
-    <row r="293" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC292" s="3"/>
+      <c r="CD292" s="3"/>
+      <c r="CE292" s="3"/>
+      <c r="CF292" s="3"/>
+      <c r="CG292" s="3"/>
+      <c r="CH292" s="3"/>
+    </row>
+    <row r="293" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -24114,8 +26081,14 @@
       <c r="BZ293" s="3"/>
       <c r="CA293" s="3"/>
       <c r="CB293" s="3"/>
-    </row>
-    <row r="294" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC293" s="3"/>
+      <c r="CD293" s="3"/>
+      <c r="CE293" s="3"/>
+      <c r="CF293" s="3"/>
+      <c r="CG293" s="3"/>
+      <c r="CH293" s="3"/>
+    </row>
+    <row r="294" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -24194,8 +26167,14 @@
       <c r="BZ294" s="3"/>
       <c r="CA294" s="3"/>
       <c r="CB294" s="3"/>
-    </row>
-    <row r="295" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC294" s="3"/>
+      <c r="CD294" s="3"/>
+      <c r="CE294" s="3"/>
+      <c r="CF294" s="3"/>
+      <c r="CG294" s="3"/>
+      <c r="CH294" s="3"/>
+    </row>
+    <row r="295" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -24274,8 +26253,14 @@
       <c r="BZ295" s="3"/>
       <c r="CA295" s="3"/>
       <c r="CB295" s="3"/>
-    </row>
-    <row r="296" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC295" s="3"/>
+      <c r="CD295" s="3"/>
+      <c r="CE295" s="3"/>
+      <c r="CF295" s="3"/>
+      <c r="CG295" s="3"/>
+      <c r="CH295" s="3"/>
+    </row>
+    <row r="296" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -24354,8 +26339,14 @@
       <c r="BZ296" s="3"/>
       <c r="CA296" s="3"/>
       <c r="CB296" s="3"/>
-    </row>
-    <row r="297" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC296" s="3"/>
+      <c r="CD296" s="3"/>
+      <c r="CE296" s="3"/>
+      <c r="CF296" s="3"/>
+      <c r="CG296" s="3"/>
+      <c r="CH296" s="3"/>
+    </row>
+    <row r="297" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -24434,8 +26425,14 @@
       <c r="BZ297" s="3"/>
       <c r="CA297" s="3"/>
       <c r="CB297" s="3"/>
-    </row>
-    <row r="298" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC297" s="3"/>
+      <c r="CD297" s="3"/>
+      <c r="CE297" s="3"/>
+      <c r="CF297" s="3"/>
+      <c r="CG297" s="3"/>
+      <c r="CH297" s="3"/>
+    </row>
+    <row r="298" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -24514,8 +26511,14 @@
       <c r="BZ298" s="3"/>
       <c r="CA298" s="3"/>
       <c r="CB298" s="3"/>
-    </row>
-    <row r="299" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC298" s="3"/>
+      <c r="CD298" s="3"/>
+      <c r="CE298" s="3"/>
+      <c r="CF298" s="3"/>
+      <c r="CG298" s="3"/>
+      <c r="CH298" s="3"/>
+    </row>
+    <row r="299" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -24594,8 +26597,14 @@
       <c r="BZ299" s="3"/>
       <c r="CA299" s="3"/>
       <c r="CB299" s="3"/>
-    </row>
-    <row r="300" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC299" s="3"/>
+      <c r="CD299" s="3"/>
+      <c r="CE299" s="3"/>
+      <c r="CF299" s="3"/>
+      <c r="CG299" s="3"/>
+      <c r="CH299" s="3"/>
+    </row>
+    <row r="300" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -24674,8 +26683,14 @@
       <c r="BZ300" s="3"/>
       <c r="CA300" s="3"/>
       <c r="CB300" s="3"/>
-    </row>
-    <row r="301" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC300" s="3"/>
+      <c r="CD300" s="3"/>
+      <c r="CE300" s="3"/>
+      <c r="CF300" s="3"/>
+      <c r="CG300" s="3"/>
+      <c r="CH300" s="3"/>
+    </row>
+    <row r="301" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -24754,8 +26769,14 @@
       <c r="BZ301" s="3"/>
       <c r="CA301" s="3"/>
       <c r="CB301" s="3"/>
-    </row>
-    <row r="302" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC301" s="3"/>
+      <c r="CD301" s="3"/>
+      <c r="CE301" s="3"/>
+      <c r="CF301" s="3"/>
+      <c r="CG301" s="3"/>
+      <c r="CH301" s="3"/>
+    </row>
+    <row r="302" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -24834,8 +26855,14 @@
       <c r="BZ302" s="3"/>
       <c r="CA302" s="3"/>
       <c r="CB302" s="3"/>
-    </row>
-    <row r="303" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC302" s="3"/>
+      <c r="CD302" s="3"/>
+      <c r="CE302" s="3"/>
+      <c r="CF302" s="3"/>
+      <c r="CG302" s="3"/>
+      <c r="CH302" s="3"/>
+    </row>
+    <row r="303" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -24914,8 +26941,14 @@
       <c r="BZ303" s="3"/>
       <c r="CA303" s="3"/>
       <c r="CB303" s="3"/>
-    </row>
-    <row r="304" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC303" s="3"/>
+      <c r="CD303" s="3"/>
+      <c r="CE303" s="3"/>
+      <c r="CF303" s="3"/>
+      <c r="CG303" s="3"/>
+      <c r="CH303" s="3"/>
+    </row>
+    <row r="304" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -24994,8 +27027,14 @@
       <c r="BZ304" s="3"/>
       <c r="CA304" s="3"/>
       <c r="CB304" s="3"/>
-    </row>
-    <row r="305" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC304" s="3"/>
+      <c r="CD304" s="3"/>
+      <c r="CE304" s="3"/>
+      <c r="CF304" s="3"/>
+      <c r="CG304" s="3"/>
+      <c r="CH304" s="3"/>
+    </row>
+    <row r="305" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -25074,8 +27113,14 @@
       <c r="BZ305" s="3"/>
       <c r="CA305" s="3"/>
       <c r="CB305" s="3"/>
-    </row>
-    <row r="306" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC305" s="3"/>
+      <c r="CD305" s="3"/>
+      <c r="CE305" s="3"/>
+      <c r="CF305" s="3"/>
+      <c r="CG305" s="3"/>
+      <c r="CH305" s="3"/>
+    </row>
+    <row r="306" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -25154,8 +27199,14 @@
       <c r="BZ306" s="3"/>
       <c r="CA306" s="3"/>
       <c r="CB306" s="3"/>
-    </row>
-    <row r="307" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC306" s="3"/>
+      <c r="CD306" s="3"/>
+      <c r="CE306" s="3"/>
+      <c r="CF306" s="3"/>
+      <c r="CG306" s="3"/>
+      <c r="CH306" s="3"/>
+    </row>
+    <row r="307" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -25234,8 +27285,14 @@
       <c r="BZ307" s="3"/>
       <c r="CA307" s="3"/>
       <c r="CB307" s="3"/>
-    </row>
-    <row r="308" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC307" s="3"/>
+      <c r="CD307" s="3"/>
+      <c r="CE307" s="3"/>
+      <c r="CF307" s="3"/>
+      <c r="CG307" s="3"/>
+      <c r="CH307" s="3"/>
+    </row>
+    <row r="308" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -25314,8 +27371,14 @@
       <c r="BZ308" s="3"/>
       <c r="CA308" s="3"/>
       <c r="CB308" s="3"/>
-    </row>
-    <row r="309" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC308" s="3"/>
+      <c r="CD308" s="3"/>
+      <c r="CE308" s="3"/>
+      <c r="CF308" s="3"/>
+      <c r="CG308" s="3"/>
+      <c r="CH308" s="3"/>
+    </row>
+    <row r="309" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -25394,8 +27457,14 @@
       <c r="BZ309" s="3"/>
       <c r="CA309" s="3"/>
       <c r="CB309" s="3"/>
-    </row>
-    <row r="310" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC309" s="3"/>
+      <c r="CD309" s="3"/>
+      <c r="CE309" s="3"/>
+      <c r="CF309" s="3"/>
+      <c r="CG309" s="3"/>
+      <c r="CH309" s="3"/>
+    </row>
+    <row r="310" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -25474,8 +27543,14 @@
       <c r="BZ310" s="3"/>
       <c r="CA310" s="3"/>
       <c r="CB310" s="3"/>
-    </row>
-    <row r="311" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC310" s="3"/>
+      <c r="CD310" s="3"/>
+      <c r="CE310" s="3"/>
+      <c r="CF310" s="3"/>
+      <c r="CG310" s="3"/>
+      <c r="CH310" s="3"/>
+    </row>
+    <row r="311" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -25554,8 +27629,14 @@
       <c r="BZ311" s="3"/>
       <c r="CA311" s="3"/>
       <c r="CB311" s="3"/>
-    </row>
-    <row r="312" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC311" s="3"/>
+      <c r="CD311" s="3"/>
+      <c r="CE311" s="3"/>
+      <c r="CF311" s="3"/>
+      <c r="CG311" s="3"/>
+      <c r="CH311" s="3"/>
+    </row>
+    <row r="312" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -25634,8 +27715,14 @@
       <c r="BZ312" s="3"/>
       <c r="CA312" s="3"/>
       <c r="CB312" s="3"/>
-    </row>
-    <row r="313" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC312" s="3"/>
+      <c r="CD312" s="3"/>
+      <c r="CE312" s="3"/>
+      <c r="CF312" s="3"/>
+      <c r="CG312" s="3"/>
+      <c r="CH312" s="3"/>
+    </row>
+    <row r="313" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -25714,8 +27801,14 @@
       <c r="BZ313" s="3"/>
       <c r="CA313" s="3"/>
       <c r="CB313" s="3"/>
-    </row>
-    <row r="314" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC313" s="3"/>
+      <c r="CD313" s="3"/>
+      <c r="CE313" s="3"/>
+      <c r="CF313" s="3"/>
+      <c r="CG313" s="3"/>
+      <c r="CH313" s="3"/>
+    </row>
+    <row r="314" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -25794,8 +27887,14 @@
       <c r="BZ314" s="3"/>
       <c r="CA314" s="3"/>
       <c r="CB314" s="3"/>
-    </row>
-    <row r="315" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC314" s="3"/>
+      <c r="CD314" s="3"/>
+      <c r="CE314" s="3"/>
+      <c r="CF314" s="3"/>
+      <c r="CG314" s="3"/>
+      <c r="CH314" s="3"/>
+    </row>
+    <row r="315" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -25874,8 +27973,14 @@
       <c r="BZ315" s="3"/>
       <c r="CA315" s="3"/>
       <c r="CB315" s="3"/>
-    </row>
-    <row r="316" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC315" s="3"/>
+      <c r="CD315" s="3"/>
+      <c r="CE315" s="3"/>
+      <c r="CF315" s="3"/>
+      <c r="CG315" s="3"/>
+      <c r="CH315" s="3"/>
+    </row>
+    <row r="316" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -25954,8 +28059,14 @@
       <c r="BZ316" s="3"/>
       <c r="CA316" s="3"/>
       <c r="CB316" s="3"/>
-    </row>
-    <row r="317" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC316" s="3"/>
+      <c r="CD316" s="3"/>
+      <c r="CE316" s="3"/>
+      <c r="CF316" s="3"/>
+      <c r="CG316" s="3"/>
+      <c r="CH316" s="3"/>
+    </row>
+    <row r="317" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -26034,8 +28145,14 @@
       <c r="BZ317" s="3"/>
       <c r="CA317" s="3"/>
       <c r="CB317" s="3"/>
-    </row>
-    <row r="318" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC317" s="3"/>
+      <c r="CD317" s="3"/>
+      <c r="CE317" s="3"/>
+      <c r="CF317" s="3"/>
+      <c r="CG317" s="3"/>
+      <c r="CH317" s="3"/>
+    </row>
+    <row r="318" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -26114,8 +28231,14 @@
       <c r="BZ318" s="3"/>
       <c r="CA318" s="3"/>
       <c r="CB318" s="3"/>
-    </row>
-    <row r="319" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC318" s="3"/>
+      <c r="CD318" s="3"/>
+      <c r="CE318" s="3"/>
+      <c r="CF318" s="3"/>
+      <c r="CG318" s="3"/>
+      <c r="CH318" s="3"/>
+    </row>
+    <row r="319" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -26194,8 +28317,14 @@
       <c r="BZ319" s="3"/>
       <c r="CA319" s="3"/>
       <c r="CB319" s="3"/>
-    </row>
-    <row r="320" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC319" s="3"/>
+      <c r="CD319" s="3"/>
+      <c r="CE319" s="3"/>
+      <c r="CF319" s="3"/>
+      <c r="CG319" s="3"/>
+      <c r="CH319" s="3"/>
+    </row>
+    <row r="320" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -26274,8 +28403,14 @@
       <c r="BZ320" s="3"/>
       <c r="CA320" s="3"/>
       <c r="CB320" s="3"/>
-    </row>
-    <row r="321" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC320" s="3"/>
+      <c r="CD320" s="3"/>
+      <c r="CE320" s="3"/>
+      <c r="CF320" s="3"/>
+      <c r="CG320" s="3"/>
+      <c r="CH320" s="3"/>
+    </row>
+    <row r="321" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -26354,8 +28489,14 @@
       <c r="BZ321" s="3"/>
       <c r="CA321" s="3"/>
       <c r="CB321" s="3"/>
-    </row>
-    <row r="322" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC321" s="3"/>
+      <c r="CD321" s="3"/>
+      <c r="CE321" s="3"/>
+      <c r="CF321" s="3"/>
+      <c r="CG321" s="3"/>
+      <c r="CH321" s="3"/>
+    </row>
+    <row r="322" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -26434,8 +28575,14 @@
       <c r="BZ322" s="3"/>
       <c r="CA322" s="3"/>
       <c r="CB322" s="3"/>
-    </row>
-    <row r="323" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC322" s="3"/>
+      <c r="CD322" s="3"/>
+      <c r="CE322" s="3"/>
+      <c r="CF322" s="3"/>
+      <c r="CG322" s="3"/>
+      <c r="CH322" s="3"/>
+    </row>
+    <row r="323" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -26514,8 +28661,14 @@
       <c r="BZ323" s="3"/>
       <c r="CA323" s="3"/>
       <c r="CB323" s="3"/>
-    </row>
-    <row r="324" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC323" s="3"/>
+      <c r="CD323" s="3"/>
+      <c r="CE323" s="3"/>
+      <c r="CF323" s="3"/>
+      <c r="CG323" s="3"/>
+      <c r="CH323" s="3"/>
+    </row>
+    <row r="324" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -26594,8 +28747,14 @@
       <c r="BZ324" s="3"/>
       <c r="CA324" s="3"/>
       <c r="CB324" s="3"/>
-    </row>
-    <row r="325" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC324" s="3"/>
+      <c r="CD324" s="3"/>
+      <c r="CE324" s="3"/>
+      <c r="CF324" s="3"/>
+      <c r="CG324" s="3"/>
+      <c r="CH324" s="3"/>
+    </row>
+    <row r="325" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -26674,8 +28833,14 @@
       <c r="BZ325" s="3"/>
       <c r="CA325" s="3"/>
       <c r="CB325" s="3"/>
-    </row>
-    <row r="326" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC325" s="3"/>
+      <c r="CD325" s="3"/>
+      <c r="CE325" s="3"/>
+      <c r="CF325" s="3"/>
+      <c r="CG325" s="3"/>
+      <c r="CH325" s="3"/>
+    </row>
+    <row r="326" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -26754,8 +28919,14 @@
       <c r="BZ326" s="3"/>
       <c r="CA326" s="3"/>
       <c r="CB326" s="3"/>
-    </row>
-    <row r="327" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC326" s="3"/>
+      <c r="CD326" s="3"/>
+      <c r="CE326" s="3"/>
+      <c r="CF326" s="3"/>
+      <c r="CG326" s="3"/>
+      <c r="CH326" s="3"/>
+    </row>
+    <row r="327" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -26834,8 +29005,14 @@
       <c r="BZ327" s="3"/>
       <c r="CA327" s="3"/>
       <c r="CB327" s="3"/>
-    </row>
-    <row r="328" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC327" s="3"/>
+      <c r="CD327" s="3"/>
+      <c r="CE327" s="3"/>
+      <c r="CF327" s="3"/>
+      <c r="CG327" s="3"/>
+      <c r="CH327" s="3"/>
+    </row>
+    <row r="328" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -26914,8 +29091,14 @@
       <c r="BZ328" s="3"/>
       <c r="CA328" s="3"/>
       <c r="CB328" s="3"/>
-    </row>
-    <row r="329" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC328" s="3"/>
+      <c r="CD328" s="3"/>
+      <c r="CE328" s="3"/>
+      <c r="CF328" s="3"/>
+      <c r="CG328" s="3"/>
+      <c r="CH328" s="3"/>
+    </row>
+    <row r="329" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -26994,8 +29177,14 @@
       <c r="BZ329" s="3"/>
       <c r="CA329" s="3"/>
       <c r="CB329" s="3"/>
-    </row>
-    <row r="330" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC329" s="3"/>
+      <c r="CD329" s="3"/>
+      <c r="CE329" s="3"/>
+      <c r="CF329" s="3"/>
+      <c r="CG329" s="3"/>
+      <c r="CH329" s="3"/>
+    </row>
+    <row r="330" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -27074,8 +29263,14 @@
       <c r="BZ330" s="3"/>
       <c r="CA330" s="3"/>
       <c r="CB330" s="3"/>
-    </row>
-    <row r="331" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC330" s="3"/>
+      <c r="CD330" s="3"/>
+      <c r="CE330" s="3"/>
+      <c r="CF330" s="3"/>
+      <c r="CG330" s="3"/>
+      <c r="CH330" s="3"/>
+    </row>
+    <row r="331" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -27154,8 +29349,14 @@
       <c r="BZ331" s="3"/>
       <c r="CA331" s="3"/>
       <c r="CB331" s="3"/>
-    </row>
-    <row r="332" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC331" s="3"/>
+      <c r="CD331" s="3"/>
+      <c r="CE331" s="3"/>
+      <c r="CF331" s="3"/>
+      <c r="CG331" s="3"/>
+      <c r="CH331" s="3"/>
+    </row>
+    <row r="332" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -27234,8 +29435,14 @@
       <c r="BZ332" s="3"/>
       <c r="CA332" s="3"/>
       <c r="CB332" s="3"/>
-    </row>
-    <row r="333" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC332" s="3"/>
+      <c r="CD332" s="3"/>
+      <c r="CE332" s="3"/>
+      <c r="CF332" s="3"/>
+      <c r="CG332" s="3"/>
+      <c r="CH332" s="3"/>
+    </row>
+    <row r="333" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -27314,8 +29521,14 @@
       <c r="BZ333" s="3"/>
       <c r="CA333" s="3"/>
       <c r="CB333" s="3"/>
-    </row>
-    <row r="334" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC333" s="3"/>
+      <c r="CD333" s="3"/>
+      <c r="CE333" s="3"/>
+      <c r="CF333" s="3"/>
+      <c r="CG333" s="3"/>
+      <c r="CH333" s="3"/>
+    </row>
+    <row r="334" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -27394,8 +29607,14 @@
       <c r="BZ334" s="3"/>
       <c r="CA334" s="3"/>
       <c r="CB334" s="3"/>
-    </row>
-    <row r="335" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC334" s="3"/>
+      <c r="CD334" s="3"/>
+      <c r="CE334" s="3"/>
+      <c r="CF334" s="3"/>
+      <c r="CG334" s="3"/>
+      <c r="CH334" s="3"/>
+    </row>
+    <row r="335" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -27474,8 +29693,14 @@
       <c r="BZ335" s="3"/>
       <c r="CA335" s="3"/>
       <c r="CB335" s="3"/>
-    </row>
-    <row r="336" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC335" s="3"/>
+      <c r="CD335" s="3"/>
+      <c r="CE335" s="3"/>
+      <c r="CF335" s="3"/>
+      <c r="CG335" s="3"/>
+      <c r="CH335" s="3"/>
+    </row>
+    <row r="336" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -27554,8 +29779,14 @@
       <c r="BZ336" s="3"/>
       <c r="CA336" s="3"/>
       <c r="CB336" s="3"/>
-    </row>
-    <row r="337" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC336" s="3"/>
+      <c r="CD336" s="3"/>
+      <c r="CE336" s="3"/>
+      <c r="CF336" s="3"/>
+      <c r="CG336" s="3"/>
+      <c r="CH336" s="3"/>
+    </row>
+    <row r="337" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -27634,8 +29865,14 @@
       <c r="BZ337" s="3"/>
       <c r="CA337" s="3"/>
       <c r="CB337" s="3"/>
-    </row>
-    <row r="338" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC337" s="3"/>
+      <c r="CD337" s="3"/>
+      <c r="CE337" s="3"/>
+      <c r="CF337" s="3"/>
+      <c r="CG337" s="3"/>
+      <c r="CH337" s="3"/>
+    </row>
+    <row r="338" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -27714,8 +29951,14 @@
       <c r="BZ338" s="3"/>
       <c r="CA338" s="3"/>
       <c r="CB338" s="3"/>
-    </row>
-    <row r="339" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC338" s="3"/>
+      <c r="CD338" s="3"/>
+      <c r="CE338" s="3"/>
+      <c r="CF338" s="3"/>
+      <c r="CG338" s="3"/>
+      <c r="CH338" s="3"/>
+    </row>
+    <row r="339" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -27794,8 +30037,14 @@
       <c r="BZ339" s="3"/>
       <c r="CA339" s="3"/>
       <c r="CB339" s="3"/>
-    </row>
-    <row r="340" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC339" s="3"/>
+      <c r="CD339" s="3"/>
+      <c r="CE339" s="3"/>
+      <c r="CF339" s="3"/>
+      <c r="CG339" s="3"/>
+      <c r="CH339" s="3"/>
+    </row>
+    <row r="340" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -27874,8 +30123,14 @@
       <c r="BZ340" s="3"/>
       <c r="CA340" s="3"/>
       <c r="CB340" s="3"/>
-    </row>
-    <row r="341" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC340" s="3"/>
+      <c r="CD340" s="3"/>
+      <c r="CE340" s="3"/>
+      <c r="CF340" s="3"/>
+      <c r="CG340" s="3"/>
+      <c r="CH340" s="3"/>
+    </row>
+    <row r="341" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -27954,8 +30209,14 @@
       <c r="BZ341" s="3"/>
       <c r="CA341" s="3"/>
       <c r="CB341" s="3"/>
-    </row>
-    <row r="342" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC341" s="3"/>
+      <c r="CD341" s="3"/>
+      <c r="CE341" s="3"/>
+      <c r="CF341" s="3"/>
+      <c r="CG341" s="3"/>
+      <c r="CH341" s="3"/>
+    </row>
+    <row r="342" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -28034,8 +30295,14 @@
       <c r="BZ342" s="3"/>
       <c r="CA342" s="3"/>
       <c r="CB342" s="3"/>
-    </row>
-    <row r="343" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC342" s="3"/>
+      <c r="CD342" s="3"/>
+      <c r="CE342" s="3"/>
+      <c r="CF342" s="3"/>
+      <c r="CG342" s="3"/>
+      <c r="CH342" s="3"/>
+    </row>
+    <row r="343" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -28114,8 +30381,14 @@
       <c r="BZ343" s="3"/>
       <c r="CA343" s="3"/>
       <c r="CB343" s="3"/>
-    </row>
-    <row r="344" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC343" s="3"/>
+      <c r="CD343" s="3"/>
+      <c r="CE343" s="3"/>
+      <c r="CF343" s="3"/>
+      <c r="CG343" s="3"/>
+      <c r="CH343" s="3"/>
+    </row>
+    <row r="344" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -28194,8 +30467,14 @@
       <c r="BZ344" s="3"/>
       <c r="CA344" s="3"/>
       <c r="CB344" s="3"/>
-    </row>
-    <row r="345" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC344" s="3"/>
+      <c r="CD344" s="3"/>
+      <c r="CE344" s="3"/>
+      <c r="CF344" s="3"/>
+      <c r="CG344" s="3"/>
+      <c r="CH344" s="3"/>
+    </row>
+    <row r="345" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -28274,8 +30553,14 @@
       <c r="BZ345" s="3"/>
       <c r="CA345" s="3"/>
       <c r="CB345" s="3"/>
-    </row>
-    <row r="346" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC345" s="3"/>
+      <c r="CD345" s="3"/>
+      <c r="CE345" s="3"/>
+      <c r="CF345" s="3"/>
+      <c r="CG345" s="3"/>
+      <c r="CH345" s="3"/>
+    </row>
+    <row r="346" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -28354,8 +30639,14 @@
       <c r="BZ346" s="3"/>
       <c r="CA346" s="3"/>
       <c r="CB346" s="3"/>
-    </row>
-    <row r="347" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC346" s="3"/>
+      <c r="CD346" s="3"/>
+      <c r="CE346" s="3"/>
+      <c r="CF346" s="3"/>
+      <c r="CG346" s="3"/>
+      <c r="CH346" s="3"/>
+    </row>
+    <row r="347" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
@@ -28434,8 +30725,14 @@
       <c r="BZ347" s="3"/>
       <c r="CA347" s="3"/>
       <c r="CB347" s="3"/>
-    </row>
-    <row r="348" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC347" s="3"/>
+      <c r="CD347" s="3"/>
+      <c r="CE347" s="3"/>
+      <c r="CF347" s="3"/>
+      <c r="CG347" s="3"/>
+      <c r="CH347" s="3"/>
+    </row>
+    <row r="348" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
@@ -28514,8 +30811,14 @@
       <c r="BZ348" s="3"/>
       <c r="CA348" s="3"/>
       <c r="CB348" s="3"/>
-    </row>
-    <row r="349" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC348" s="3"/>
+      <c r="CD348" s="3"/>
+      <c r="CE348" s="3"/>
+      <c r="CF348" s="3"/>
+      <c r="CG348" s="3"/>
+      <c r="CH348" s="3"/>
+    </row>
+    <row r="349" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="3"/>
@@ -28594,8 +30897,14 @@
       <c r="BZ349" s="3"/>
       <c r="CA349" s="3"/>
       <c r="CB349" s="3"/>
-    </row>
-    <row r="350" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC349" s="3"/>
+      <c r="CD349" s="3"/>
+      <c r="CE349" s="3"/>
+      <c r="CF349" s="3"/>
+      <c r="CG349" s="3"/>
+      <c r="CH349" s="3"/>
+    </row>
+    <row r="350" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
@@ -28674,8 +30983,14 @@
       <c r="BZ350" s="3"/>
       <c r="CA350" s="3"/>
       <c r="CB350" s="3"/>
-    </row>
-    <row r="351" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC350" s="3"/>
+      <c r="CD350" s="3"/>
+      <c r="CE350" s="3"/>
+      <c r="CF350" s="3"/>
+      <c r="CG350" s="3"/>
+      <c r="CH350" s="3"/>
+    </row>
+    <row r="351" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C351" s="3"/>
       <c r="D351" s="3"/>
       <c r="E351" s="3"/>
@@ -28754,8 +31069,14 @@
       <c r="BZ351" s="3"/>
       <c r="CA351" s="3"/>
       <c r="CB351" s="3"/>
-    </row>
-    <row r="352" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC351" s="3"/>
+      <c r="CD351" s="3"/>
+      <c r="CE351" s="3"/>
+      <c r="CF351" s="3"/>
+      <c r="CG351" s="3"/>
+      <c r="CH351" s="3"/>
+    </row>
+    <row r="352" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C352" s="3"/>
       <c r="D352" s="3"/>
       <c r="E352" s="3"/>
@@ -28834,8 +31155,14 @@
       <c r="BZ352" s="3"/>
       <c r="CA352" s="3"/>
       <c r="CB352" s="3"/>
-    </row>
-    <row r="353" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC352" s="3"/>
+      <c r="CD352" s="3"/>
+      <c r="CE352" s="3"/>
+      <c r="CF352" s="3"/>
+      <c r="CG352" s="3"/>
+      <c r="CH352" s="3"/>
+    </row>
+    <row r="353" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C353" s="3"/>
       <c r="D353" s="3"/>
       <c r="E353" s="3"/>
@@ -28914,8 +31241,14 @@
       <c r="BZ353" s="3"/>
       <c r="CA353" s="3"/>
       <c r="CB353" s="3"/>
-    </row>
-    <row r="354" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC353" s="3"/>
+      <c r="CD353" s="3"/>
+      <c r="CE353" s="3"/>
+      <c r="CF353" s="3"/>
+      <c r="CG353" s="3"/>
+      <c r="CH353" s="3"/>
+    </row>
+    <row r="354" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C354" s="3"/>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -28994,8 +31327,14 @@
       <c r="BZ354" s="3"/>
       <c r="CA354" s="3"/>
       <c r="CB354" s="3"/>
-    </row>
-    <row r="355" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC354" s="3"/>
+      <c r="CD354" s="3"/>
+      <c r="CE354" s="3"/>
+      <c r="CF354" s="3"/>
+      <c r="CG354" s="3"/>
+      <c r="CH354" s="3"/>
+    </row>
+    <row r="355" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C355" s="3"/>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -29074,8 +31413,14 @@
       <c r="BZ355" s="3"/>
       <c r="CA355" s="3"/>
       <c r="CB355" s="3"/>
-    </row>
-    <row r="356" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC355" s="3"/>
+      <c r="CD355" s="3"/>
+      <c r="CE355" s="3"/>
+      <c r="CF355" s="3"/>
+      <c r="CG355" s="3"/>
+      <c r="CH355" s="3"/>
+    </row>
+    <row r="356" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
@@ -29154,8 +31499,14 @@
       <c r="BZ356" s="3"/>
       <c r="CA356" s="3"/>
       <c r="CB356" s="3"/>
-    </row>
-    <row r="357" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC356" s="3"/>
+      <c r="CD356" s="3"/>
+      <c r="CE356" s="3"/>
+      <c r="CF356" s="3"/>
+      <c r="CG356" s="3"/>
+      <c r="CH356" s="3"/>
+    </row>
+    <row r="357" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
       <c r="E357" s="3"/>
@@ -29234,8 +31585,14 @@
       <c r="BZ357" s="3"/>
       <c r="CA357" s="3"/>
       <c r="CB357" s="3"/>
-    </row>
-    <row r="358" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC357" s="3"/>
+      <c r="CD357" s="3"/>
+      <c r="CE357" s="3"/>
+      <c r="CF357" s="3"/>
+      <c r="CG357" s="3"/>
+      <c r="CH357" s="3"/>
+    </row>
+    <row r="358" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
@@ -29314,8 +31671,14 @@
       <c r="BZ358" s="3"/>
       <c r="CA358" s="3"/>
       <c r="CB358" s="3"/>
-    </row>
-    <row r="359" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC358" s="3"/>
+      <c r="CD358" s="3"/>
+      <c r="CE358" s="3"/>
+      <c r="CF358" s="3"/>
+      <c r="CG358" s="3"/>
+      <c r="CH358" s="3"/>
+    </row>
+    <row r="359" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
       <c r="E359" s="3"/>
@@ -29394,8 +31757,14 @@
       <c r="BZ359" s="3"/>
       <c r="CA359" s="3"/>
       <c r="CB359" s="3"/>
-    </row>
-    <row r="360" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC359" s="3"/>
+      <c r="CD359" s="3"/>
+      <c r="CE359" s="3"/>
+      <c r="CF359" s="3"/>
+      <c r="CG359" s="3"/>
+      <c r="CH359" s="3"/>
+    </row>
+    <row r="360" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C360" s="3"/>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
@@ -29474,8 +31843,14 @@
       <c r="BZ360" s="3"/>
       <c r="CA360" s="3"/>
       <c r="CB360" s="3"/>
-    </row>
-    <row r="361" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC360" s="3"/>
+      <c r="CD360" s="3"/>
+      <c r="CE360" s="3"/>
+      <c r="CF360" s="3"/>
+      <c r="CG360" s="3"/>
+      <c r="CH360" s="3"/>
+    </row>
+    <row r="361" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C361" s="3"/>
       <c r="D361" s="3"/>
       <c r="E361" s="3"/>
@@ -29554,8 +31929,14 @@
       <c r="BZ361" s="3"/>
       <c r="CA361" s="3"/>
       <c r="CB361" s="3"/>
-    </row>
-    <row r="362" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC361" s="3"/>
+      <c r="CD361" s="3"/>
+      <c r="CE361" s="3"/>
+      <c r="CF361" s="3"/>
+      <c r="CG361" s="3"/>
+      <c r="CH361" s="3"/>
+    </row>
+    <row r="362" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
@@ -29634,8 +32015,14 @@
       <c r="BZ362" s="3"/>
       <c r="CA362" s="3"/>
       <c r="CB362" s="3"/>
-    </row>
-    <row r="363" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC362" s="3"/>
+      <c r="CD362" s="3"/>
+      <c r="CE362" s="3"/>
+      <c r="CF362" s="3"/>
+      <c r="CG362" s="3"/>
+      <c r="CH362" s="3"/>
+    </row>
+    <row r="363" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C363" s="3"/>
       <c r="D363" s="3"/>
       <c r="E363" s="3"/>
@@ -29714,8 +32101,14 @@
       <c r="BZ363" s="3"/>
       <c r="CA363" s="3"/>
       <c r="CB363" s="3"/>
-    </row>
-    <row r="364" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC363" s="3"/>
+      <c r="CD363" s="3"/>
+      <c r="CE363" s="3"/>
+      <c r="CF363" s="3"/>
+      <c r="CG363" s="3"/>
+      <c r="CH363" s="3"/>
+    </row>
+    <row r="364" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C364" s="3"/>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
@@ -29794,8 +32187,14 @@
       <c r="BZ364" s="3"/>
       <c r="CA364" s="3"/>
       <c r="CB364" s="3"/>
-    </row>
-    <row r="365" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC364" s="3"/>
+      <c r="CD364" s="3"/>
+      <c r="CE364" s="3"/>
+      <c r="CF364" s="3"/>
+      <c r="CG364" s="3"/>
+      <c r="CH364" s="3"/>
+    </row>
+    <row r="365" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C365" s="3"/>
       <c r="D365" s="3"/>
       <c r="E365" s="3"/>
@@ -29874,8 +32273,14 @@
       <c r="BZ365" s="3"/>
       <c r="CA365" s="3"/>
       <c r="CB365" s="3"/>
-    </row>
-    <row r="366" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC365" s="3"/>
+      <c r="CD365" s="3"/>
+      <c r="CE365" s="3"/>
+      <c r="CF365" s="3"/>
+      <c r="CG365" s="3"/>
+      <c r="CH365" s="3"/>
+    </row>
+    <row r="366" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
@@ -29954,8 +32359,14 @@
       <c r="BZ366" s="3"/>
       <c r="CA366" s="3"/>
       <c r="CB366" s="3"/>
-    </row>
-    <row r="367" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC366" s="3"/>
+      <c r="CD366" s="3"/>
+      <c r="CE366" s="3"/>
+      <c r="CF366" s="3"/>
+      <c r="CG366" s="3"/>
+      <c r="CH366" s="3"/>
+    </row>
+    <row r="367" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
       <c r="E367" s="3"/>
@@ -30034,8 +32445,14 @@
       <c r="BZ367" s="3"/>
       <c r="CA367" s="3"/>
       <c r="CB367" s="3"/>
-    </row>
-    <row r="368" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC367" s="3"/>
+      <c r="CD367" s="3"/>
+      <c r="CE367" s="3"/>
+      <c r="CF367" s="3"/>
+      <c r="CG367" s="3"/>
+      <c r="CH367" s="3"/>
+    </row>
+    <row r="368" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
       <c r="E368" s="3"/>
@@ -30114,8 +32531,14 @@
       <c r="BZ368" s="3"/>
       <c r="CA368" s="3"/>
       <c r="CB368" s="3"/>
-    </row>
-    <row r="369" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC368" s="3"/>
+      <c r="CD368" s="3"/>
+      <c r="CE368" s="3"/>
+      <c r="CF368" s="3"/>
+      <c r="CG368" s="3"/>
+      <c r="CH368" s="3"/>
+    </row>
+    <row r="369" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
       <c r="E369" s="3"/>
@@ -30194,8 +32617,14 @@
       <c r="BZ369" s="3"/>
       <c r="CA369" s="3"/>
       <c r="CB369" s="3"/>
-    </row>
-    <row r="370" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC369" s="3"/>
+      <c r="CD369" s="3"/>
+      <c r="CE369" s="3"/>
+      <c r="CF369" s="3"/>
+      <c r="CG369" s="3"/>
+      <c r="CH369" s="3"/>
+    </row>
+    <row r="370" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
@@ -30274,8 +32703,14 @@
       <c r="BZ370" s="3"/>
       <c r="CA370" s="3"/>
       <c r="CB370" s="3"/>
-    </row>
-    <row r="371" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC370" s="3"/>
+      <c r="CD370" s="3"/>
+      <c r="CE370" s="3"/>
+      <c r="CF370" s="3"/>
+      <c r="CG370" s="3"/>
+      <c r="CH370" s="3"/>
+    </row>
+    <row r="371" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C371" s="3"/>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
@@ -30354,8 +32789,14 @@
       <c r="BZ371" s="3"/>
       <c r="CA371" s="3"/>
       <c r="CB371" s="3"/>
-    </row>
-    <row r="372" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC371" s="3"/>
+      <c r="CD371" s="3"/>
+      <c r="CE371" s="3"/>
+      <c r="CF371" s="3"/>
+      <c r="CG371" s="3"/>
+      <c r="CH371" s="3"/>
+    </row>
+    <row r="372" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
@@ -30434,8 +32875,14 @@
       <c r="BZ372" s="3"/>
       <c r="CA372" s="3"/>
       <c r="CB372" s="3"/>
-    </row>
-    <row r="373" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC372" s="3"/>
+      <c r="CD372" s="3"/>
+      <c r="CE372" s="3"/>
+      <c r="CF372" s="3"/>
+      <c r="CG372" s="3"/>
+      <c r="CH372" s="3"/>
+    </row>
+    <row r="373" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C373" s="3"/>
       <c r="D373" s="3"/>
       <c r="E373" s="3"/>
@@ -30514,8 +32961,14 @@
       <c r="BZ373" s="3"/>
       <c r="CA373" s="3"/>
       <c r="CB373" s="3"/>
-    </row>
-    <row r="374" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC373" s="3"/>
+      <c r="CD373" s="3"/>
+      <c r="CE373" s="3"/>
+      <c r="CF373" s="3"/>
+      <c r="CG373" s="3"/>
+      <c r="CH373" s="3"/>
+    </row>
+    <row r="374" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
@@ -30594,8 +33047,14 @@
       <c r="BZ374" s="3"/>
       <c r="CA374" s="3"/>
       <c r="CB374" s="3"/>
-    </row>
-    <row r="375" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC374" s="3"/>
+      <c r="CD374" s="3"/>
+      <c r="CE374" s="3"/>
+      <c r="CF374" s="3"/>
+      <c r="CG374" s="3"/>
+      <c r="CH374" s="3"/>
+    </row>
+    <row r="375" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C375" s="3"/>
       <c r="D375" s="3"/>
       <c r="E375" s="3"/>
@@ -30674,8 +33133,14 @@
       <c r="BZ375" s="3"/>
       <c r="CA375" s="3"/>
       <c r="CB375" s="3"/>
-    </row>
-    <row r="376" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC375" s="3"/>
+      <c r="CD375" s="3"/>
+      <c r="CE375" s="3"/>
+      <c r="CF375" s="3"/>
+      <c r="CG375" s="3"/>
+      <c r="CH375" s="3"/>
+    </row>
+    <row r="376" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
@@ -30754,8 +33219,14 @@
       <c r="BZ376" s="3"/>
       <c r="CA376" s="3"/>
       <c r="CB376" s="3"/>
-    </row>
-    <row r="377" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC376" s="3"/>
+      <c r="CD376" s="3"/>
+      <c r="CE376" s="3"/>
+      <c r="CF376" s="3"/>
+      <c r="CG376" s="3"/>
+      <c r="CH376" s="3"/>
+    </row>
+    <row r="377" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
       <c r="E377" s="3"/>
@@ -30834,8 +33305,14 @@
       <c r="BZ377" s="3"/>
       <c r="CA377" s="3"/>
       <c r="CB377" s="3"/>
-    </row>
-    <row r="378" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC377" s="3"/>
+      <c r="CD377" s="3"/>
+      <c r="CE377" s="3"/>
+      <c r="CF377" s="3"/>
+      <c r="CG377" s="3"/>
+      <c r="CH377" s="3"/>
+    </row>
+    <row r="378" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
@@ -30914,8 +33391,14 @@
       <c r="BZ378" s="3"/>
       <c r="CA378" s="3"/>
       <c r="CB378" s="3"/>
-    </row>
-    <row r="379" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC378" s="3"/>
+      <c r="CD378" s="3"/>
+      <c r="CE378" s="3"/>
+      <c r="CF378" s="3"/>
+      <c r="CG378" s="3"/>
+      <c r="CH378" s="3"/>
+    </row>
+    <row r="379" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="3"/>
@@ -30994,8 +33477,14 @@
       <c r="BZ379" s="3"/>
       <c r="CA379" s="3"/>
       <c r="CB379" s="3"/>
-    </row>
-    <row r="380" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC379" s="3"/>
+      <c r="CD379" s="3"/>
+      <c r="CE379" s="3"/>
+      <c r="CF379" s="3"/>
+      <c r="CG379" s="3"/>
+      <c r="CH379" s="3"/>
+    </row>
+    <row r="380" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
@@ -31074,8 +33563,14 @@
       <c r="BZ380" s="3"/>
       <c r="CA380" s="3"/>
       <c r="CB380" s="3"/>
-    </row>
-    <row r="381" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC380" s="3"/>
+      <c r="CD380" s="3"/>
+      <c r="CE380" s="3"/>
+      <c r="CF380" s="3"/>
+      <c r="CG380" s="3"/>
+      <c r="CH380" s="3"/>
+    </row>
+    <row r="381" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="3"/>
@@ -31154,8 +33649,14 @@
       <c r="BZ381" s="3"/>
       <c r="CA381" s="3"/>
       <c r="CB381" s="3"/>
-    </row>
-    <row r="382" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC381" s="3"/>
+      <c r="CD381" s="3"/>
+      <c r="CE381" s="3"/>
+      <c r="CF381" s="3"/>
+      <c r="CG381" s="3"/>
+      <c r="CH381" s="3"/>
+    </row>
+    <row r="382" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
@@ -31234,8 +33735,14 @@
       <c r="BZ382" s="3"/>
       <c r="CA382" s="3"/>
       <c r="CB382" s="3"/>
-    </row>
-    <row r="383" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC382" s="3"/>
+      <c r="CD382" s="3"/>
+      <c r="CE382" s="3"/>
+      <c r="CF382" s="3"/>
+      <c r="CG382" s="3"/>
+      <c r="CH382" s="3"/>
+    </row>
+    <row r="383" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
       <c r="E383" s="3"/>
@@ -31314,8 +33821,14 @@
       <c r="BZ383" s="3"/>
       <c r="CA383" s="3"/>
       <c r="CB383" s="3"/>
-    </row>
-    <row r="384" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC383" s="3"/>
+      <c r="CD383" s="3"/>
+      <c r="CE383" s="3"/>
+      <c r="CF383" s="3"/>
+      <c r="CG383" s="3"/>
+      <c r="CH383" s="3"/>
+    </row>
+    <row r="384" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
@@ -31394,8 +33907,14 @@
       <c r="BZ384" s="3"/>
       <c r="CA384" s="3"/>
       <c r="CB384" s="3"/>
-    </row>
-    <row r="385" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC384" s="3"/>
+      <c r="CD384" s="3"/>
+      <c r="CE384" s="3"/>
+      <c r="CF384" s="3"/>
+      <c r="CG384" s="3"/>
+      <c r="CH384" s="3"/>
+    </row>
+    <row r="385" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
       <c r="E385" s="3"/>
@@ -31474,8 +33993,14 @@
       <c r="BZ385" s="3"/>
       <c r="CA385" s="3"/>
       <c r="CB385" s="3"/>
-    </row>
-    <row r="386" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC385" s="3"/>
+      <c r="CD385" s="3"/>
+      <c r="CE385" s="3"/>
+      <c r="CF385" s="3"/>
+      <c r="CG385" s="3"/>
+      <c r="CH385" s="3"/>
+    </row>
+    <row r="386" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
@@ -31554,8 +34079,14 @@
       <c r="BZ386" s="3"/>
       <c r="CA386" s="3"/>
       <c r="CB386" s="3"/>
-    </row>
-    <row r="387" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC386" s="3"/>
+      <c r="CD386" s="3"/>
+      <c r="CE386" s="3"/>
+      <c r="CF386" s="3"/>
+      <c r="CG386" s="3"/>
+      <c r="CH386" s="3"/>
+    </row>
+    <row r="387" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="3"/>
@@ -31634,8 +34165,14 @@
       <c r="BZ387" s="3"/>
       <c r="CA387" s="3"/>
       <c r="CB387" s="3"/>
-    </row>
-    <row r="388" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC387" s="3"/>
+      <c r="CD387" s="3"/>
+      <c r="CE387" s="3"/>
+      <c r="CF387" s="3"/>
+      <c r="CG387" s="3"/>
+      <c r="CH387" s="3"/>
+    </row>
+    <row r="388" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
@@ -31714,8 +34251,14 @@
       <c r="BZ388" s="3"/>
       <c r="CA388" s="3"/>
       <c r="CB388" s="3"/>
-    </row>
-    <row r="389" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC388" s="3"/>
+      <c r="CD388" s="3"/>
+      <c r="CE388" s="3"/>
+      <c r="CF388" s="3"/>
+      <c r="CG388" s="3"/>
+      <c r="CH388" s="3"/>
+    </row>
+    <row r="389" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
       <c r="E389" s="3"/>
@@ -31794,8 +34337,14 @@
       <c r="BZ389" s="3"/>
       <c r="CA389" s="3"/>
       <c r="CB389" s="3"/>
-    </row>
-    <row r="390" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC389" s="3"/>
+      <c r="CD389" s="3"/>
+      <c r="CE389" s="3"/>
+      <c r="CF389" s="3"/>
+      <c r="CG389" s="3"/>
+      <c r="CH389" s="3"/>
+    </row>
+    <row r="390" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
@@ -31874,8 +34423,14 @@
       <c r="BZ390" s="3"/>
       <c r="CA390" s="3"/>
       <c r="CB390" s="3"/>
-    </row>
-    <row r="391" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC390" s="3"/>
+      <c r="CD390" s="3"/>
+      <c r="CE390" s="3"/>
+      <c r="CF390" s="3"/>
+      <c r="CG390" s="3"/>
+      <c r="CH390" s="3"/>
+    </row>
+    <row r="391" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
       <c r="E391" s="3"/>
@@ -31954,8 +34509,14 @@
       <c r="BZ391" s="3"/>
       <c r="CA391" s="3"/>
       <c r="CB391" s="3"/>
-    </row>
-    <row r="392" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC391" s="3"/>
+      <c r="CD391" s="3"/>
+      <c r="CE391" s="3"/>
+      <c r="CF391" s="3"/>
+      <c r="CG391" s="3"/>
+      <c r="CH391" s="3"/>
+    </row>
+    <row r="392" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
@@ -32034,8 +34595,14 @@
       <c r="BZ392" s="3"/>
       <c r="CA392" s="3"/>
       <c r="CB392" s="3"/>
-    </row>
-    <row r="393" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC392" s="3"/>
+      <c r="CD392" s="3"/>
+      <c r="CE392" s="3"/>
+      <c r="CF392" s="3"/>
+      <c r="CG392" s="3"/>
+      <c r="CH392" s="3"/>
+    </row>
+    <row r="393" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
       <c r="E393" s="3"/>
@@ -32114,8 +34681,14 @@
       <c r="BZ393" s="3"/>
       <c r="CA393" s="3"/>
       <c r="CB393" s="3"/>
-    </row>
-    <row r="394" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC393" s="3"/>
+      <c r="CD393" s="3"/>
+      <c r="CE393" s="3"/>
+      <c r="CF393" s="3"/>
+      <c r="CG393" s="3"/>
+      <c r="CH393" s="3"/>
+    </row>
+    <row r="394" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
@@ -32194,8 +34767,14 @@
       <c r="BZ394" s="3"/>
       <c r="CA394" s="3"/>
       <c r="CB394" s="3"/>
-    </row>
-    <row r="395" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC394" s="3"/>
+      <c r="CD394" s="3"/>
+      <c r="CE394" s="3"/>
+      <c r="CF394" s="3"/>
+      <c r="CG394" s="3"/>
+      <c r="CH394" s="3"/>
+    </row>
+    <row r="395" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
       <c r="E395" s="3"/>
@@ -32274,8 +34853,14 @@
       <c r="BZ395" s="3"/>
       <c r="CA395" s="3"/>
       <c r="CB395" s="3"/>
-    </row>
-    <row r="396" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC395" s="3"/>
+      <c r="CD395" s="3"/>
+      <c r="CE395" s="3"/>
+      <c r="CF395" s="3"/>
+      <c r="CG395" s="3"/>
+      <c r="CH395" s="3"/>
+    </row>
+    <row r="396" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
@@ -32354,8 +34939,14 @@
       <c r="BZ396" s="3"/>
       <c r="CA396" s="3"/>
       <c r="CB396" s="3"/>
-    </row>
-    <row r="397" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC396" s="3"/>
+      <c r="CD396" s="3"/>
+      <c r="CE396" s="3"/>
+      <c r="CF396" s="3"/>
+      <c r="CG396" s="3"/>
+      <c r="CH396" s="3"/>
+    </row>
+    <row r="397" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
       <c r="E397" s="3"/>
@@ -32434,8 +35025,14 @@
       <c r="BZ397" s="3"/>
       <c r="CA397" s="3"/>
       <c r="CB397" s="3"/>
-    </row>
-    <row r="398" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC397" s="3"/>
+      <c r="CD397" s="3"/>
+      <c r="CE397" s="3"/>
+      <c r="CF397" s="3"/>
+      <c r="CG397" s="3"/>
+      <c r="CH397" s="3"/>
+    </row>
+    <row r="398" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
@@ -32514,8 +35111,14 @@
       <c r="BZ398" s="3"/>
       <c r="CA398" s="3"/>
       <c r="CB398" s="3"/>
-    </row>
-    <row r="399" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC398" s="3"/>
+      <c r="CD398" s="3"/>
+      <c r="CE398" s="3"/>
+      <c r="CF398" s="3"/>
+      <c r="CG398" s="3"/>
+      <c r="CH398" s="3"/>
+    </row>
+    <row r="399" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
       <c r="E399" s="3"/>
@@ -32594,8 +35197,14 @@
       <c r="BZ399" s="3"/>
       <c r="CA399" s="3"/>
       <c r="CB399" s="3"/>
-    </row>
-    <row r="400" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC399" s="3"/>
+      <c r="CD399" s="3"/>
+      <c r="CE399" s="3"/>
+      <c r="CF399" s="3"/>
+      <c r="CG399" s="3"/>
+      <c r="CH399" s="3"/>
+    </row>
+    <row r="400" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
@@ -32674,8 +35283,14 @@
       <c r="BZ400" s="3"/>
       <c r="CA400" s="3"/>
       <c r="CB400" s="3"/>
-    </row>
-    <row r="401" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC400" s="3"/>
+      <c r="CD400" s="3"/>
+      <c r="CE400" s="3"/>
+      <c r="CF400" s="3"/>
+      <c r="CG400" s="3"/>
+      <c r="CH400" s="3"/>
+    </row>
+    <row r="401" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
       <c r="E401" s="3"/>
@@ -32754,8 +35369,14 @@
       <c r="BZ401" s="3"/>
       <c r="CA401" s="3"/>
       <c r="CB401" s="3"/>
-    </row>
-    <row r="402" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC401" s="3"/>
+      <c r="CD401" s="3"/>
+      <c r="CE401" s="3"/>
+      <c r="CF401" s="3"/>
+      <c r="CG401" s="3"/>
+      <c r="CH401" s="3"/>
+    </row>
+    <row r="402" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
@@ -32834,8 +35455,14 @@
       <c r="BZ402" s="3"/>
       <c r="CA402" s="3"/>
       <c r="CB402" s="3"/>
-    </row>
-    <row r="403" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC402" s="3"/>
+      <c r="CD402" s="3"/>
+      <c r="CE402" s="3"/>
+      <c r="CF402" s="3"/>
+      <c r="CG402" s="3"/>
+      <c r="CH402" s="3"/>
+    </row>
+    <row r="403" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C403" s="3"/>
       <c r="D403" s="3"/>
       <c r="E403" s="3"/>
@@ -32914,8 +35541,14 @@
       <c r="BZ403" s="3"/>
       <c r="CA403" s="3"/>
       <c r="CB403" s="3"/>
-    </row>
-    <row r="404" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC403" s="3"/>
+      <c r="CD403" s="3"/>
+      <c r="CE403" s="3"/>
+      <c r="CF403" s="3"/>
+      <c r="CG403" s="3"/>
+      <c r="CH403" s="3"/>
+    </row>
+    <row r="404" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C404" s="3"/>
       <c r="D404" s="3"/>
       <c r="E404" s="3"/>
@@ -32994,8 +35627,14 @@
       <c r="BZ404" s="3"/>
       <c r="CA404" s="3"/>
       <c r="CB404" s="3"/>
-    </row>
-    <row r="405" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC404" s="3"/>
+      <c r="CD404" s="3"/>
+      <c r="CE404" s="3"/>
+      <c r="CF404" s="3"/>
+      <c r="CG404" s="3"/>
+      <c r="CH404" s="3"/>
+    </row>
+    <row r="405" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C405" s="3"/>
       <c r="D405" s="3"/>
       <c r="E405" s="3"/>
@@ -33074,8 +35713,14 @@
       <c r="BZ405" s="3"/>
       <c r="CA405" s="3"/>
       <c r="CB405" s="3"/>
-    </row>
-    <row r="406" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC405" s="3"/>
+      <c r="CD405" s="3"/>
+      <c r="CE405" s="3"/>
+      <c r="CF405" s="3"/>
+      <c r="CG405" s="3"/>
+      <c r="CH405" s="3"/>
+    </row>
+    <row r="406" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C406" s="3"/>
       <c r="D406" s="3"/>
       <c r="E406" s="3"/>
@@ -33154,8 +35799,14 @@
       <c r="BZ406" s="3"/>
       <c r="CA406" s="3"/>
       <c r="CB406" s="3"/>
-    </row>
-    <row r="407" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC406" s="3"/>
+      <c r="CD406" s="3"/>
+      <c r="CE406" s="3"/>
+      <c r="CF406" s="3"/>
+      <c r="CG406" s="3"/>
+      <c r="CH406" s="3"/>
+    </row>
+    <row r="407" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C407" s="3"/>
       <c r="D407" s="3"/>
       <c r="E407" s="3"/>
@@ -33234,8 +35885,14 @@
       <c r="BZ407" s="3"/>
       <c r="CA407" s="3"/>
       <c r="CB407" s="3"/>
-    </row>
-    <row r="408" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC407" s="3"/>
+      <c r="CD407" s="3"/>
+      <c r="CE407" s="3"/>
+      <c r="CF407" s="3"/>
+      <c r="CG407" s="3"/>
+      <c r="CH407" s="3"/>
+    </row>
+    <row r="408" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C408" s="3"/>
       <c r="D408" s="3"/>
       <c r="E408" s="3"/>
@@ -33314,8 +35971,14 @@
       <c r="BZ408" s="3"/>
       <c r="CA408" s="3"/>
       <c r="CB408" s="3"/>
-    </row>
-    <row r="409" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC408" s="3"/>
+      <c r="CD408" s="3"/>
+      <c r="CE408" s="3"/>
+      <c r="CF408" s="3"/>
+      <c r="CG408" s="3"/>
+      <c r="CH408" s="3"/>
+    </row>
+    <row r="409" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C409" s="3"/>
       <c r="D409" s="3"/>
       <c r="E409" s="3"/>
@@ -33394,8 +36057,14 @@
       <c r="BZ409" s="3"/>
       <c r="CA409" s="3"/>
       <c r="CB409" s="3"/>
-    </row>
-    <row r="410" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC409" s="3"/>
+      <c r="CD409" s="3"/>
+      <c r="CE409" s="3"/>
+      <c r="CF409" s="3"/>
+      <c r="CG409" s="3"/>
+      <c r="CH409" s="3"/>
+    </row>
+    <row r="410" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C410" s="3"/>
       <c r="D410" s="3"/>
       <c r="E410" s="3"/>
@@ -33474,8 +36143,14 @@
       <c r="BZ410" s="3"/>
       <c r="CA410" s="3"/>
       <c r="CB410" s="3"/>
-    </row>
-    <row r="411" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC410" s="3"/>
+      <c r="CD410" s="3"/>
+      <c r="CE410" s="3"/>
+      <c r="CF410" s="3"/>
+      <c r="CG410" s="3"/>
+      <c r="CH410" s="3"/>
+    </row>
+    <row r="411" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C411" s="3"/>
       <c r="D411" s="3"/>
       <c r="E411" s="3"/>
@@ -33554,8 +36229,14 @@
       <c r="BZ411" s="3"/>
       <c r="CA411" s="3"/>
       <c r="CB411" s="3"/>
-    </row>
-    <row r="412" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC411" s="3"/>
+      <c r="CD411" s="3"/>
+      <c r="CE411" s="3"/>
+      <c r="CF411" s="3"/>
+      <c r="CG411" s="3"/>
+      <c r="CH411" s="3"/>
+    </row>
+    <row r="412" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C412" s="3"/>
       <c r="D412" s="3"/>
       <c r="E412" s="3"/>
@@ -33634,8 +36315,14 @@
       <c r="BZ412" s="3"/>
       <c r="CA412" s="3"/>
       <c r="CB412" s="3"/>
-    </row>
-    <row r="413" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC412" s="3"/>
+      <c r="CD412" s="3"/>
+      <c r="CE412" s="3"/>
+      <c r="CF412" s="3"/>
+      <c r="CG412" s="3"/>
+      <c r="CH412" s="3"/>
+    </row>
+    <row r="413" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C413" s="3"/>
       <c r="D413" s="3"/>
       <c r="E413" s="3"/>
@@ -33714,8 +36401,14 @@
       <c r="BZ413" s="3"/>
       <c r="CA413" s="3"/>
       <c r="CB413" s="3"/>
-    </row>
-    <row r="414" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC413" s="3"/>
+      <c r="CD413" s="3"/>
+      <c r="CE413" s="3"/>
+      <c r="CF413" s="3"/>
+      <c r="CG413" s="3"/>
+      <c r="CH413" s="3"/>
+    </row>
+    <row r="414" spans="3:86" x14ac:dyDescent="0.2">
       <c r="C414" s="3"/>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
@@ -33794,6 +36487,12 @@
       <c r="BZ414" s="3"/>
       <c r="CA414" s="3"/>
       <c r="CB414" s="3"/>
+      <c r="CC414" s="3"/>
+      <c r="CD414" s="3"/>
+      <c r="CE414" s="3"/>
+      <c r="CF414" s="3"/>
+      <c r="CG414" s="3"/>
+      <c r="CH414" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
